--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -564,7 +564,7 @@
         <v>43598</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>45203</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>43360</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44452</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45203</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>43382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43431</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43461</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43594</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>43882</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44043</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44148</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44221</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44446</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44450</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44589</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44755</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44762</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44805</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44813</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44886</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44894</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44938</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45016</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>43319</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>43319</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>43325</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>43327</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>43327</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>43332</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>43340</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>43341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>43346</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>43348</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>43349</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43350</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>43353</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>43353</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>43353</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>43360</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>43361</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>43362</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>43363</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43369</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>43370</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>43374</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43374</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>43374</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>43374</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>43382</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>43390</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>43390</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>43392</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>43392</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>43392</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>43392</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>43392</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>43392</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>43395</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>43397</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>43405</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>43405</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>43406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>43410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43416</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>43416</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>43416</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>43416</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>43416</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>43419</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43419</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>43419</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43431</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43437</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>43445</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>43453</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>43461</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>43461</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>43462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>43467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>43467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>43475</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>43476</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>43479</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>43479</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>43483</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>43485</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>43487</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>43490</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>43493</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>43494</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>43494</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>43494</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>43494</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>43494</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>43502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>43502</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>43507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>43507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>43515</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>43515</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>43524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>43528</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>43542</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43544</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43546</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43547</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>43547</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>43559</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>43560</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>43563</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>43566</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>43567</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>43570</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43570</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>43578</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>43581</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>43584</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>43584</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>43584</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43591</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>43594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>43594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>43594</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43594</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>43594</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43594</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43594</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43594</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43598</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>43598</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>43598</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>43598</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>43598</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>43605</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>43606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>43606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>43606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>43606</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>43607</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>43612</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>43615</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>43629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>43635</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>43636</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43640</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>43644</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>43648</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>43648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>43648</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>43648</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>43653</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>43654</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>43656</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>43658</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>43665</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>43672</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>43676</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>43676</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>43684</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>43700</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>43713</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>43720</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>43725</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>43727</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>43732</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43733</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43738</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43738</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43740</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>43741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43742</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>43742</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>43746</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>43749</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>43753</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43754</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43766</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>43768</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>43770</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>43773</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43774</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43785</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43788</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43789</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43794</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43797</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43803</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43808</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43808</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43808</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43808</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43808</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43808</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43811</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43837</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43838</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43838</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43838</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>43844</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>43845</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>43845</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>43846</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43847</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43848</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43850</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43850</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43851</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43853</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43857</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43857</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43861</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43864</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43866</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43870</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43878</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43879</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43881</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43883</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43888</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43891</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43891</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43894</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>43895</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>43895</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>43896</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>43899</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>43899</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43899</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43901</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43905</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43906</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>43907</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>43907</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43910</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43913</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>43913</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>43913</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>43913</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>43913</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>43913</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>43913</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>43916</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>43916</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>43916</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>43920</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>43921</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>43922</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>43923</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>43923</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>43945</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>43945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>43956</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>43968</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>43978</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>43978</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>43983</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>43983</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>43997</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>43997</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44004</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44004</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44014</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44026</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44032</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44040</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44040</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44050</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44050</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44050</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44053</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44053</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44057</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44064</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44067</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44069</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44070</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44076</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44076</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44082</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44084</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44090</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44092</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44095</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44100</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44102</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44102</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44103</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44103</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44105</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44106</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44110</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44112</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44112</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44112</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44117</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44124</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44124</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44124</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44127</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44130</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44130</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44134</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44137</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44137</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44139</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44144</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44145</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44145</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44146</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44154</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44155</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44161</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44161</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44161</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44168</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>44175</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44183</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44189</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44193</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44193</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44193</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44204</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44206</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44207</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44208</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44209</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44211</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44216</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44217</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44218</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44221</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44221</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44221</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44221</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44221</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44221</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>44221</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44223</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44223</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44224</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44229</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44229</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44231</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44235</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44238</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44242</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44246</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44247</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44251</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44263</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44264</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44266</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44270</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44271</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44280</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44284</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44285</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44287</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44294</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44299</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>44301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44307</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44316</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44319</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44321</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44321</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44322</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44322</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44328</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44334</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44334</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>44340</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>44343</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44344</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44344</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44347</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44351</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44354</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>44358</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44362</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>44362</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44368</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44368</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44370</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44377</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44378</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44378</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44378</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44378</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44385</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44385</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44385</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>44385</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44385</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44386</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44389</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44389</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44389</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>44389</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>44389</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44389</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>44389</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>44392</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44392</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>44392</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44392</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44392</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44392</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44392</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44392</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44392</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44392</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44400</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>44403</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44404</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44412</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44417</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44418</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>44419</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44419</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44419</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44421</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>44423</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>44424</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44424</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>44425</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44431</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44434</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44434</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>44434</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>44435</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>44435</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44435</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44438</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44439</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44439</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44440</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44445</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>44446</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44448</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44448</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44448</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44449</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>44449</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>44450</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>44454</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44456</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44462</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44463</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44463</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44466</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44467</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44467</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44468</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44468</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44473</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44473</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>44475</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44480</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>44487</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44487</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>44487</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44488</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44488</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44489</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44490</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>44491</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44494</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44501</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>44505</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44505</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44508</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44509</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44509</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>44509</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44509</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44509</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44509</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44509</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44511</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>44512</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>44512</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44512</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44512</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44518</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44523</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44523</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44523</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44523</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44523</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44524</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44526</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44528</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44537</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44538</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>44538</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44543</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44546</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>44550</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44550</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44550</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44550</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44550</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44550</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44552</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44552</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>44552</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44557</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44564</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44564</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44564</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44564</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44564</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44572</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44574</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44580</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44580</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44580</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44580</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44581</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44581</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44581</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44582</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44582</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44587</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44596</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44602</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44602</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44603</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44606</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44607</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44607</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44607</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44608</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44608</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44610</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44615</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44616</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44616</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44620</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44623</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44624</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44627</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44627</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44629</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44629</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44629</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44629</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>44629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44634</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>44635</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>44641</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44641</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44643</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44644</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44649</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44649</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44655</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>44656</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44658</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44658</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44659</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44659</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44663</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44665</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44671</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>44671</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>44676</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>44678</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>44679</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44679</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44683</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>44686</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44698</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44699</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44709</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44711</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44719</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>44719</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44719</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44720</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>44734</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>44735</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44735</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44745</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44745</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44745</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44748</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44748</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44750</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44758</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44759</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44762</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44762</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44763</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44763</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44764</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44776</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44777</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44780</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44780</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44780</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44784</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44785</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>44787</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>44787</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44787</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>44787</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44787</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>44802</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>44806</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44806</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44810</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44812</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>44812</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44813</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44813</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44819</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>44819</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>44819</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>44820</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44820</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44820</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44823</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44823</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44823</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44824</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>44824</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>44825</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>44826</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44827</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44829</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44829</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44830</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44830</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44831</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44840</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44840</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44840</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>44846</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44846</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44846</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>44846</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>44846</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44852</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44853</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44853</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44854</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44858</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44861</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44861</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44862</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44864</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44866</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44867</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>44868</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>44868</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44868</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44662,7 +44662,7 @@
         <v>44872</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>44872</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>44875</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44876</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>44876</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>44876</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>44876</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>44879</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>44880</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>44880</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>44881</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>44881</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>44881</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>44881</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>44881</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44881</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44885</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>44886</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>44886</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44894</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>44894</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44894</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44895</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>44896</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44896</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44900</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>44900</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>44900</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>44900</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44909</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>44910</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>44910</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44911</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>44911</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>44916</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44916</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>44917</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44921</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>44924</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44929</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44936</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>44936</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44936</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44937</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>44938</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44938</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44943</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44943</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44943</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44943</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44945</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>44945</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44946</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44949</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>44950</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>44952</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44952</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>44952</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>44959</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>44960</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44970</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44973</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44976</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>44977</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>44977</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>44980</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44980</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44980</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>44980</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44982</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>44985</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>44988</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>44993</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>44993</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>44993</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>44994</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>44994</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44998</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44998</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44999</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>44999</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45000</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45005</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45005</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45006</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45009</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45012</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45012</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45012</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45012</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45013</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45015</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45021</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45025</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45029</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45029</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45033</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45033</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45033</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45033</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45033</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45035</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45037</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45040</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45040</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45040</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45040</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45040</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45041</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45041</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45041</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45044</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45050</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45050</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45050</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45056</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>45056</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45057</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>45058</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>45061</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45062</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45063</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45063</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45065</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45065</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45068</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45068</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45070</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45070</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45071</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45072</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45075</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45078</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45078</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45079</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45081</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45082</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45082</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45085</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45085</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45086</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45089</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45089</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45092</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45092</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45093</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45093</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45095</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45096</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45096</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45098</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>45098</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45098</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45098</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45098</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45099</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>45099</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45099</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45099</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45099</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45099</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45105</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45105</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45106</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45106</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45106</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45106</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>45106</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45107</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45107</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45107</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45107</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45107</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45113</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45113</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>45113</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>45113</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45113</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45113</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45119</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45119</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45120</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45120</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45123</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45127</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45127</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45133</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45137</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45138</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45140</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45141</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45146</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45146</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45146</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45147</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45147</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45148</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45149</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45149</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>45149</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>45154</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45156</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>45156</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45156</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45159</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>45161</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>45161</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45162</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56665,7 +56665,7 @@
         <v>45164</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45167</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45168</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         <v>45168</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45168</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>45169</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45170</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45170</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45170</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45170</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45170</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45171</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45171</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45173</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45173</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45173</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45173</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>45176</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45176</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45180</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45180</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45183</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45186</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45189</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45189</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45189</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45189</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58229,7 +58229,7 @@
         <v>45189</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45189</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45189</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>45189</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58457,7 +58457,7 @@
         <v>45189</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>45191</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45191</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>45191</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45191</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>45194</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45194</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>45194</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45194</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>45197</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45201</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45202</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         <v>45203</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>45203</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45203</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>45203</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45204</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>45204</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45205</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         <v>45208</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45208</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45210</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45211</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45211</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45212</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45215</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45221</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>45222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45222</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         <v>45222</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45222</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>45223</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>45223</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45226</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60445,14 +60445,14 @@
     <row r="1032" ht="15" customHeight="1">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>A 53303-2023</t>
+          <t>A 53300-2023</t>
         </is>
       </c>
       <c r="B1032" s="1" t="n">
         <v>45229</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         </is>
       </c>
       <c r="G1032" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -60502,14 +60502,14 @@
     <row r="1033" ht="15" customHeight="1">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>A 53300-2023</t>
+          <t>A 53303-2023</t>
         </is>
       </c>
       <c r="B1033" s="1" t="n">
         <v>45229</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         </is>
       </c>
       <c r="G1033" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="H1033" t="n">
         <v>0</v>
@@ -60566,7 +60566,7 @@
         <v>45231</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -60623,7 +60623,7 @@
         <v>45233</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>45237</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -60730,14 +60730,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 55274-2023</t>
+          <t>A 56475-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -60787,14 +60787,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 56452-2023</t>
+          <t>A 56485-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>7.1</v>
+        <v>1</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -60844,14 +60844,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 56498-2023</t>
+          <t>A 56506-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -60901,14 +60901,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 56479-2023</t>
+          <t>A 56452-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -60921,7 +60921,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>3.2</v>
+        <v>7.1</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -60958,14 +60958,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 56489-2023</t>
+          <t>A 56498-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -61015,14 +61015,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 56475-2023</t>
+          <t>A 55274-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61035,7 +61035,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -61072,14 +61072,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 56485-2023</t>
+          <t>A 56479-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61092,7 +61092,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -61129,14 +61129,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 56506-2023</t>
+          <t>A 56489-2023</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -61193,7 +61193,7 @@
         <v>45238</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>45239</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -61307,7 +61307,7 @@
         <v>45239</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45239</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>45242</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -61478,7 +61478,7 @@
         <v>45245</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -61540,7 +61540,7 @@
         <v>45246</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -61597,7 +61597,7 @@
         <v>45246</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -61654,7 +61654,7 @@
         <v>45249</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -61704,14 +61704,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 58602-2023</t>
+          <t>A 58653-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -61724,7 +61724,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -61768,7 +61768,7 @@
         <v>45251</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -61823,14 +61823,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 58653-2023</t>
+          <t>A 58602-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -61843,7 +61843,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -61887,7 +61887,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -61937,14 +61937,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 59203-2023</t>
+          <t>A 59312-2023</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -61957,7 +61957,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>4.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -61994,14 +61994,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59216-2023</t>
+          <t>A 59438-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>2.1</v>
+        <v>19.9</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -62051,14 +62051,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 59312-2023</t>
+          <t>A 59203-2023</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>8.699999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -62108,14 +62108,14 @@
     <row r="1061" ht="15" customHeight="1">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>A 59438-2023</t>
+          <t>A 59216-2023</t>
         </is>
       </c>
       <c r="B1061" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         </is>
       </c>
       <c r="G1061" t="n">
-        <v>19.9</v>
+        <v>2.1</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -62165,14 +62165,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 60019-2023</t>
+          <t>A 60018-2023</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62185,7 +62185,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -62222,14 +62222,14 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>A 60018-2023</t>
+          <t>A 60019-2023</t>
         </is>
       </c>
       <c r="B1063" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         </is>
       </c>
       <c r="G1063" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -564,7 +564,7 @@
         <v>43598</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>45203</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>43360</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44452</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45203</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>43382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43431</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43461</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43594</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>43882</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44043</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44148</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44221</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44446</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44450</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44589</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44755</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44762</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44805</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44813</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44886</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44894</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44938</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45016</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>43319</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>43319</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>43325</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>43327</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>43327</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>43332</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>43340</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>43341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>43346</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>43348</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>43349</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43350</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>43353</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>43353</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>43353</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>43360</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>43361</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>43362</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>43363</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43369</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>43370</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>43374</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43374</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>43374</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>43374</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>43382</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>43390</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>43390</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>43392</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>43392</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>43392</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>43392</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>43392</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>43392</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>43395</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>43397</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>43405</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>43405</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>43406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>43410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43416</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>43416</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>43416</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>43416</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>43416</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>43419</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43419</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>43419</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43431</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43437</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>43445</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>43453</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>43461</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>43461</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>43462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>43467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>43467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>43475</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>43476</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>43479</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>43479</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>43483</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>43485</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>43487</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>43490</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>43493</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>43494</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>43494</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>43494</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>43494</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>43494</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>43502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>43502</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>43507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>43507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>43515</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>43515</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>43524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>43528</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>43542</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43544</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43546</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43547</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>43547</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>43559</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>43560</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>43563</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>43566</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>43567</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>43570</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43570</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>43578</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>43581</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>43584</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>43584</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>43584</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43591</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>43594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>43594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>43594</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43594</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>43594</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43594</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43594</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43594</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43598</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>43598</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>43598</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>43598</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>43598</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>43605</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>43606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>43606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>43606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>43606</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>43607</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>43612</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>43615</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>43629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>43635</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>43636</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43640</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>43644</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>43648</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>43648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>43648</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>43648</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>43653</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>43654</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>43656</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>43658</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>43665</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>43672</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>43676</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>43676</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>43684</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>43700</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>43713</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>43720</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>43725</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>43727</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>43732</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43733</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43738</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43738</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43740</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>43741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43742</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>43742</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>43746</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>43749</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>43753</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43754</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43766</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>43768</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>43770</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>43773</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43774</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43785</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43788</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43789</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43794</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43797</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43803</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43808</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43808</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43808</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43808</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43808</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43808</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43811</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43837</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43838</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43838</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43838</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>43844</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>43845</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>43845</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>43846</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43847</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43848</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43850</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43850</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43851</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43853</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43857</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43857</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43861</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43864</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43866</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43870</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43878</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43879</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43881</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43883</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43888</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43891</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43891</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43894</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>43895</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>43895</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>43896</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>43899</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>43899</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43899</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43901</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43905</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43906</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>43907</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>43907</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43910</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43913</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>43913</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>43913</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>43913</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>43913</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>43913</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>43913</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>43916</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>43916</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>43916</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>43920</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>43921</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>43922</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>43923</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>43923</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>43945</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>43945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>43956</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>43968</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>43978</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>43978</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>43983</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>43983</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>43997</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>43997</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44004</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44004</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44014</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44026</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44032</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44040</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44040</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44050</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44050</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44050</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44053</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44053</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44057</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44064</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44067</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44069</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44070</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44076</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44076</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44082</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44084</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44090</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44092</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44095</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44100</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44102</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44102</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44103</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44103</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44105</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44106</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44110</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44112</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44112</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44112</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44117</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44124</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44124</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44124</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44127</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44130</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44130</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44134</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44137</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44137</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44139</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44144</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44145</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44145</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44146</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44154</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44155</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44161</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44161</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44161</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44168</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>44175</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44183</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44189</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44193</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44193</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44193</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44204</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44206</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44207</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44208</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44209</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44211</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44216</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44217</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44218</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44221</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44221</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44221</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44221</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44221</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44221</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>44221</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44223</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44223</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44224</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44229</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44229</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44231</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44235</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44238</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44242</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44246</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44247</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44251</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44263</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44264</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44266</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44270</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44271</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44280</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44284</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44285</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44287</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44294</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44299</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>44301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44307</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44316</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44319</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44321</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44321</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44322</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44322</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44328</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44334</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44334</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>44340</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>44343</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44344</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44344</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44347</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44351</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44354</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>44358</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44362</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>44362</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44368</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44368</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44370</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44377</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44378</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44378</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44378</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44378</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44385</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44385</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44385</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>44385</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44385</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44386</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44389</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44389</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44389</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>44389</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>44389</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44389</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>44389</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>44392</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44392</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>44392</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44392</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44392</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44392</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44392</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44392</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44392</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44392</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44400</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>44403</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44404</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44412</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44417</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44418</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>44419</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44419</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44419</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44421</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>44423</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>44424</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44424</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>44425</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44431</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44434</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44434</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>44434</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>44435</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>44435</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44435</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44438</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44439</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44439</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44440</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44445</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>44446</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44448</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44448</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44448</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44449</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>44449</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>44450</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>44454</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44456</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44462</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44463</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44463</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44466</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44467</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44467</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44468</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44468</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44473</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44473</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>44475</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44480</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>44487</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44487</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>44487</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44488</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44488</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44489</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44490</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>44491</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44494</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44501</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>44505</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44505</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44508</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44509</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44509</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>44509</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44509</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44509</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44509</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44509</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44511</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>44512</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>44512</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44512</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44512</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44518</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44523</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44523</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44523</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44523</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44523</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44524</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44526</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44528</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44537</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44538</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>44538</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44543</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44546</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>44550</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44550</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44550</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44550</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44550</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44550</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44552</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44552</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>44552</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44557</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44564</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44564</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44564</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44564</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44564</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44572</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44574</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44580</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44580</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44580</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44580</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44581</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44581</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44581</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44582</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44582</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44587</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44596</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44602</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44602</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44603</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44606</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44607</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44607</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44607</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44608</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44608</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44610</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44615</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44616</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44616</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44620</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44623</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44624</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44627</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44627</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44629</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44629</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44629</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44629</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>44629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44634</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>44635</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>44641</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44641</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44643</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44644</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44649</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44649</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44655</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>44656</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44658</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44658</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44659</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44659</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44663</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44665</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44671</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>44671</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>44676</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>44678</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>44679</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44679</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44683</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>44686</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44698</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44699</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44709</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44711</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44719</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>44719</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44719</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44720</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>44734</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>44735</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44735</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44745</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44745</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44745</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44748</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44748</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44750</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44758</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44759</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44762</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44762</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44763</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44763</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44764</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44776</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44777</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44780</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44780</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44780</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44784</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44785</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>44787</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>44787</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44787</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>44787</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44787</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>44802</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>44806</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44806</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44810</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44812</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>44812</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44813</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44813</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44819</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>44819</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>44819</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>44820</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44820</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44820</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44823</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44823</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44823</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44824</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>44824</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>44825</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>44826</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44827</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44829</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44829</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44830</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44830</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44831</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44840</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44840</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44840</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>44846</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44846</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44846</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>44846</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>44846</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44852</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44853</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44853</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44854</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44858</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44861</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44861</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44862</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44864</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44866</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44867</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>44868</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>44868</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44868</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44662,7 +44662,7 @@
         <v>44872</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>44872</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>44875</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44876</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>44876</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>44876</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>44876</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>44879</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>44880</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>44880</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>44881</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>44881</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>44881</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>44881</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>44881</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44881</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44885</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>44886</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>44886</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44894</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>44894</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44894</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44895</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>44896</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44896</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44900</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>44900</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>44900</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>44900</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44909</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>44910</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>44910</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44911</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>44911</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>44916</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44916</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>44917</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44921</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>44924</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44929</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44936</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>44936</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44936</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44937</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>44938</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44938</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44943</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44943</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44943</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44943</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44945</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>44945</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44946</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44949</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>44950</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>44952</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44952</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>44952</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>44959</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>44960</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44970</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44973</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44976</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>44977</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>44977</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>44980</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44980</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44980</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>44980</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44982</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>44985</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>44988</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>44993</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>44993</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>44993</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>44994</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>44994</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44998</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44998</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44999</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>44999</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45000</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45005</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45005</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45006</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45009</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45012</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45012</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45012</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45012</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45013</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45015</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45021</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45025</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45029</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45029</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45033</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45033</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45033</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45033</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45033</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45035</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45037</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45040</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45040</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45040</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45040</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45040</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45041</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45041</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45041</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45044</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45050</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45050</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45050</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45056</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>45056</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45057</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>45058</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>45061</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45062</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45063</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45063</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45065</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45065</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45068</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45068</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45070</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45070</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45071</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45072</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45075</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45078</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45078</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45079</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45081</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45082</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45082</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45085</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45085</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45086</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45089</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45089</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45092</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45092</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45093</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45093</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45095</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45096</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45096</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45098</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>45098</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45098</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45098</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45098</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45099</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>45099</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45099</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45099</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45099</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45099</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45105</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45105</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45106</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45106</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45106</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45106</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>45106</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45107</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45107</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45107</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45107</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45107</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45113</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45113</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>45113</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>45113</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45113</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45113</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45119</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45119</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45120</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45120</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45123</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45127</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45127</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45133</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45137</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45138</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45140</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45141</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45146</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45146</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45146</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45147</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45147</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45148</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45149</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45149</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>45149</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>45154</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45156</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>45156</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45156</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45159</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>45161</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>45161</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45162</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56665,7 +56665,7 @@
         <v>45164</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45167</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45168</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         <v>45168</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45168</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>45169</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45170</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45170</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45170</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45170</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45170</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45171</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45171</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45173</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45173</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45173</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45173</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>45176</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45176</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45180</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45180</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45183</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45186</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45189</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45189</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45189</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45189</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58229,7 +58229,7 @@
         <v>45189</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45189</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45189</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>45189</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58457,7 +58457,7 @@
         <v>45189</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>45191</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45191</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>45191</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45191</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>45194</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45194</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>45194</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45194</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>45197</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45201</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45202</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         <v>45203</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>45203</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45203</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>45203</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45204</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>45204</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45205</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         <v>45208</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45208</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45210</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45211</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45211</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45212</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45215</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45221</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>45222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45222</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         <v>45222</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45222</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>45223</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>45223</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45226</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45229</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>45229</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45231</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -60623,7 +60623,7 @@
         <v>45233</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>45237</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -60730,14 +60730,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 56475-2023</t>
+          <t>A 55274-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -60787,14 +60787,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 56485-2023</t>
+          <t>A 56475-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -60844,14 +60844,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 56506-2023</t>
+          <t>A 56485-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -60901,14 +60901,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 56452-2023</t>
+          <t>A 56479-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -60921,7 +60921,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>7.1</v>
+        <v>3.2</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -60958,14 +60958,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 56498-2023</t>
+          <t>A 56489-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -61015,14 +61015,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 55274-2023</t>
+          <t>A 56506-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61035,7 +61035,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -61072,14 +61072,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 56479-2023</t>
+          <t>A 56452-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61092,7 +61092,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>3.2</v>
+        <v>7.1</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -61129,14 +61129,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 56489-2023</t>
+          <t>A 56498-2023</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -61193,7 +61193,7 @@
         <v>45238</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>45239</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -61307,7 +61307,7 @@
         <v>45239</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45239</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>45242</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -61478,7 +61478,7 @@
         <v>45245</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -61533,14 +61533,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 57577-2023</t>
+          <t>A 57544-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -61553,7 +61553,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -61590,14 +61590,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 57544-2023</t>
+          <t>A 57577-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -61610,7 +61610,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -61654,7 +61654,7 @@
         <v>45249</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>45251</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -61761,14 +61761,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 58646-2023</t>
+          <t>A 58602-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -61780,13 +61780,8 @@
           <t>SÄFFLE</t>
         </is>
       </c>
-      <c r="F1055" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G1055" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -61823,14 +61818,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 58602-2023</t>
+          <t>A 58646-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -61842,8 +61837,13 @@
           <t>SÄFFLE</t>
         </is>
       </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G1056" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -61887,7 +61887,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -61944,7 +61944,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -61994,14 +61994,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59438-2023</t>
+          <t>A 59203-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>19.9</v>
+        <v>4.8</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -62051,14 +62051,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 59203-2023</t>
+          <t>A 59216-2023</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -62108,14 +62108,14 @@
     <row r="1061" ht="15" customHeight="1">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>A 59216-2023</t>
+          <t>A 59438-2023</t>
         </is>
       </c>
       <c r="B1061" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         </is>
       </c>
       <c r="G1061" t="n">
-        <v>2.1</v>
+        <v>19.9</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -62172,7 +62172,7 @@
         <v>45258</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45258</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -564,7 +564,7 @@
         <v>43598</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>45203</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>43360</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44452</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45203</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>43382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43431</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43461</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43594</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>43882</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44043</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44148</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44221</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44446</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44450</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44589</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44755</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44762</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44805</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44813</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44886</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44894</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44938</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45016</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>43319</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>43319</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>43325</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>43327</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>43327</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>43332</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>43340</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>43341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>43346</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>43348</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>43349</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43350</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>43353</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>43353</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>43353</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>43360</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>43361</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>43362</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>43363</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43369</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>43370</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>43374</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43374</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>43374</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>43374</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>43382</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>43390</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>43390</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>43392</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>43392</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>43392</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>43392</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>43392</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>43392</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>43395</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>43397</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>43405</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>43405</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>43406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>43410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43416</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>43416</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>43416</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>43416</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>43416</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>43419</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43419</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>43419</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43431</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43437</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>43445</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>43453</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>43461</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>43461</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>43462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>43467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>43467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>43475</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>43476</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>43479</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>43479</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>43483</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>43485</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>43487</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>43490</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>43493</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>43494</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>43494</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>43494</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>43494</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>43494</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>43502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>43502</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>43507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>43507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>43515</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>43515</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>43524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>43528</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>43542</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43544</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43546</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43547</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>43547</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>43559</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>43560</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>43563</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>43566</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>43567</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>43570</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43570</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>43578</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>43581</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>43584</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>43584</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>43584</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43591</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>43594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>43594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>43594</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43594</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>43594</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43594</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43594</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43594</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43598</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>43598</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>43598</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>43598</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>43598</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>43605</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>43606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>43606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>43606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>43606</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>43607</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>43612</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>43615</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>43629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>43635</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>43636</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43640</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>43644</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>43648</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>43648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>43648</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>43648</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>43653</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>43654</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>43656</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>43658</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>43665</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>43672</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>43676</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>43676</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>43684</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>43700</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>43713</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>43720</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>43725</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>43727</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>43732</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43733</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43738</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43738</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43740</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>43741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43742</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>43742</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>43746</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>43749</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>43753</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43754</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43766</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>43768</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>43770</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>43773</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43774</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43785</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43788</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43789</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43794</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43797</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43803</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43808</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43808</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43808</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43808</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43808</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43808</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43811</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43837</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43838</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43838</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43838</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>43844</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>43845</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>43845</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>43846</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43847</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43848</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43850</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43850</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43851</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43853</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43857</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43857</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43861</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43864</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43866</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43870</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43878</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43879</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43881</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43883</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43888</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43891</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43891</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43894</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>43895</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>43895</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>43896</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>43899</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>43899</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43899</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43901</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43905</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43906</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>43907</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>43907</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43910</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43913</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>43913</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>43913</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>43913</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>43913</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>43913</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>43913</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>43916</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>43916</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>43916</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>43920</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>43921</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>43922</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>43923</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>43923</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>43945</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>43945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>43956</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>43968</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>43978</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>43978</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>43983</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>43983</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>43997</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>43997</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44004</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44004</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44014</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44026</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44032</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44040</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44040</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44050</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44050</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44050</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44053</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44053</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44057</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44064</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44067</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44069</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44070</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44076</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44076</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44082</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44084</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44090</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44092</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44095</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44100</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44102</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44102</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44103</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44103</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44105</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44106</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44110</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44112</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44112</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44112</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44117</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44124</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44124</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44124</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44127</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44130</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44130</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44134</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44137</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44137</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44139</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44144</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44145</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44145</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44146</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44154</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44155</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44161</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44161</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44161</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44168</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>44175</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44183</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44189</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44193</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44193</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44193</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44204</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44206</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44207</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44208</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44209</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44211</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44216</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44217</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44218</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44221</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44221</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44221</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44221</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44221</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44221</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>44221</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44223</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44223</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44224</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44229</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44229</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44231</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44235</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44238</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44242</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44246</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44247</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44251</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44263</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44264</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44266</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44270</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44271</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44280</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44284</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44285</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44287</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44294</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44299</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>44301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44307</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44316</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44319</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44321</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44321</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44322</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44322</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44328</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44334</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44334</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>44340</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>44343</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44344</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44344</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44347</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44351</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44354</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>44358</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44362</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>44362</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44368</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44368</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44370</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44377</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44378</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44378</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44378</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44378</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44385</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44385</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44385</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>44385</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44385</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44386</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44389</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44389</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44389</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>44389</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>44389</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44389</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>44389</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>44392</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44392</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>44392</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44392</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44392</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44392</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44392</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44392</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44392</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44392</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44400</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>44403</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44404</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44412</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44417</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44418</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>44419</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44419</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44419</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44421</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>44423</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>44424</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44424</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>44425</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44431</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44434</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44434</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>44434</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>44435</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>44435</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44435</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44438</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44439</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44439</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44440</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44445</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>44446</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44448</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44448</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44448</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44449</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>44449</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>44450</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>44454</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44456</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44462</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44463</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44463</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44466</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44467</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44467</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44468</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44468</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44473</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44473</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>44475</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44480</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>44487</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44487</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>44487</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44488</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44488</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44489</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44490</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>44491</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44494</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44501</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>44505</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44505</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44508</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44509</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44509</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>44509</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44509</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44509</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44509</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44509</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44511</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>44512</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>44512</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44512</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44512</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44518</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44523</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44523</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44523</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44523</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44523</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44524</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44526</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44528</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44537</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44538</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>44538</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44543</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44546</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>44550</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44550</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44550</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44550</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44550</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44550</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44552</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44552</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>44552</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44557</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44564</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44564</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44564</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44564</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44564</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44572</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44574</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44580</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44580</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44580</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44580</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44581</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44581</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44581</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44582</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44582</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44587</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44596</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44602</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44602</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44603</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44606</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44607</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44607</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44607</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44608</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44608</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44610</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44615</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44616</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44616</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44620</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44623</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44624</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44627</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44627</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44629</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44629</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44629</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44629</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>44629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44634</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>44635</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>44641</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44641</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44643</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44644</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44649</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44649</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44655</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>44656</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44658</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44658</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44659</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44659</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44663</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44665</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44671</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>44671</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>44676</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>44678</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>44679</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44679</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44683</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>44686</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44698</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44699</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44709</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44711</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44719</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>44719</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44719</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44720</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>44734</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>44735</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44735</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44745</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44745</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44745</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44748</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44748</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44750</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44758</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44759</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44762</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44762</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44763</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44763</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44764</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44776</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44777</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44780</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44780</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44780</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44784</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44785</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>44787</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>44787</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44787</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>44787</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44787</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>44802</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>44806</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44806</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44810</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44812</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>44812</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44813</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44813</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44819</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>44819</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>44819</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>44820</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44820</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44820</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44823</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44823</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44823</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44824</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>44824</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>44825</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>44826</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44827</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44829</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44829</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44830</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44830</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44831</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44840</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44840</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44840</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>44846</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44846</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44846</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>44846</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>44846</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44852</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44853</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44853</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44854</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44858</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44861</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44861</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44862</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44864</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44866</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44867</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>44868</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>44868</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44868</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44662,7 +44662,7 @@
         <v>44872</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>44872</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>44875</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44876</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>44876</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>44876</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>44876</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>44879</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>44880</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>44880</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>44881</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>44881</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>44881</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>44881</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>44881</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44881</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44885</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>44886</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>44886</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44894</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>44894</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44894</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44895</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>44896</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44896</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44900</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>44900</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>44900</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>44900</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44909</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>44910</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>44910</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44911</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>44911</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>44916</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44916</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>44917</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44921</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>44924</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44929</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44936</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>44936</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44936</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44937</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>44938</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44938</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44943</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44943</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44943</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44943</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44945</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>44945</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44946</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44949</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>44950</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>44952</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44952</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>44952</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>44959</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>44960</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44970</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44973</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44976</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>44977</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>44977</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>44980</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44980</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44980</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>44980</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44982</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>44985</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>44988</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>44993</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>44993</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>44993</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>44994</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>44994</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44998</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44998</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44999</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>44999</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45000</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45005</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45005</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45006</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45009</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45012</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45012</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45012</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45012</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45013</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45015</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45021</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45025</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45029</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45029</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45033</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45033</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45033</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45033</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45033</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45035</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45037</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45040</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45040</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45040</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45040</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45040</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45041</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45041</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45041</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45044</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45050</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45050</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45050</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45056</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>45056</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45057</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>45058</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>45061</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45062</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45063</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45063</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45065</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45065</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45068</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45068</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45070</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45070</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45071</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45072</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45075</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45078</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45078</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45079</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45081</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45082</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45082</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45085</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45085</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45086</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45089</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45089</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45092</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45092</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45093</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45093</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45095</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45096</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45096</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45098</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>45098</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45098</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45098</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45098</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45099</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>45099</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45099</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45099</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45099</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45099</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45105</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45105</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45106</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45106</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45106</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45106</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>45106</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45107</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45107</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45107</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45107</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45107</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45113</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45113</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>45113</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>45113</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45113</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45113</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45119</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45119</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45120</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45120</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45123</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45127</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45127</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45133</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45137</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45138</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45140</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45141</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45146</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45146</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45146</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45147</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45147</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45148</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45149</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45149</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>45149</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>45154</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45156</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>45156</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45156</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45159</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>45161</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>45161</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45162</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56665,7 +56665,7 @@
         <v>45164</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45167</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45168</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         <v>45168</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45168</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>45169</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45170</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45170</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45170</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45170</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45170</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45171</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45171</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45173</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45173</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45173</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45173</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>45176</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45176</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45180</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45180</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45183</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45186</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45189</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45189</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45189</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45189</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58229,7 +58229,7 @@
         <v>45189</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45189</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45189</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>45189</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58457,7 +58457,7 @@
         <v>45189</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>45191</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45191</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>45191</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45191</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>45194</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45194</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>45194</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45194</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>45197</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45201</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45202</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         <v>45203</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>45203</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45203</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>45203</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45204</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>45204</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45205</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         <v>45208</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45208</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45210</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45211</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45211</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45212</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45215</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45221</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>45222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45222</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         <v>45222</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45222</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>45223</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>45223</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45226</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45229</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>45229</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45231</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -60623,7 +60623,7 @@
         <v>45233</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -60673,14 +60673,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 55223-2023</t>
+          <t>A 55274-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -60693,7 +60693,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>7.5</v>
+        <v>0.7</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -60730,14 +60730,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 55274-2023</t>
+          <t>A 55223-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>0.7</v>
+        <v>7.5</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -60787,14 +60787,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 56475-2023</t>
+          <t>A 56452-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -60844,14 +60844,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 56485-2023</t>
+          <t>A 56498-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -60901,14 +60901,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 56479-2023</t>
+          <t>A 56475-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -60921,7 +60921,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -60958,14 +60958,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 56489-2023</t>
+          <t>A 56485-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -61015,14 +61015,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 56506-2023</t>
+          <t>A 56479-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61035,7 +61035,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -61072,14 +61072,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 56452-2023</t>
+          <t>A 56489-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61092,7 +61092,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>7.1</v>
+        <v>2.7</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -61129,14 +61129,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 56498-2023</t>
+          <t>A 56506-2023</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -61193,7 +61193,7 @@
         <v>45238</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>45239</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -61307,7 +61307,7 @@
         <v>45239</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45239</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>45242</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -61478,7 +61478,7 @@
         <v>45245</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -61540,7 +61540,7 @@
         <v>45246</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -61597,7 +61597,7 @@
         <v>45246</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -61654,7 +61654,7 @@
         <v>45249</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -61704,14 +61704,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 58653-2023</t>
+          <t>A 58602-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -61724,7 +61724,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -61761,14 +61761,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 58602-2023</t>
+          <t>A 58653-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -61781,7 +61781,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -61825,7 +61825,7 @@
         <v>45251</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -61887,7 +61887,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -61944,7 +61944,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -62001,7 +62001,7 @@
         <v>45253</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62058,7 +62058,7 @@
         <v>45253</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62115,7 +62115,7 @@
         <v>45253</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62165,14 +62165,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 60018-2023</t>
+          <t>A 60019-2023</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62185,7 +62185,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -62222,14 +62222,14 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>A 60019-2023</t>
+          <t>A 60018-2023</t>
         </is>
       </c>
       <c r="B1063" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         </is>
       </c>
       <c r="G1063" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -564,7 +564,7 @@
         <v>43598</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>45203</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>43360</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44452</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45203</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>43382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43431</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43461</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43594</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>43882</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44043</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44148</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44221</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44446</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44450</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44589</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44755</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44762</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44805</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44813</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44886</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44894</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44938</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45016</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>43319</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>43319</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>43325</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>43327</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>43327</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>43332</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>43340</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>43341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>43346</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>43348</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>43349</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43350</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>43353</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>43353</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>43353</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>43360</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>43361</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>43362</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>43363</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43369</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>43370</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>43374</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43374</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>43374</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>43374</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>43382</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>43390</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>43390</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>43392</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>43392</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>43392</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>43392</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>43392</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>43392</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>43395</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>43397</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>43405</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>43405</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>43406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>43410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43416</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>43416</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>43416</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>43416</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>43416</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>43419</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43419</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>43419</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43431</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43437</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>43445</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>43453</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>43461</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>43461</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>43462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>43467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>43467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>43475</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>43476</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>43479</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>43479</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>43483</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>43485</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>43487</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>43490</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>43493</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>43494</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>43494</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>43494</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>43494</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>43494</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>43502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>43502</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>43507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>43507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>43515</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>43515</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>43524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>43528</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>43542</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43544</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43546</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43547</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>43547</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>43559</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>43560</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>43563</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>43566</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>43567</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>43570</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43570</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>43578</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>43581</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>43584</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>43584</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>43584</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43591</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>43594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>43594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>43594</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43594</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>43594</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43594</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43594</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43594</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43598</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>43598</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>43598</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>43598</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>43598</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>43605</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>43606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>43606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>43606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>43606</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>43607</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>43612</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>43615</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>43629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>43635</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>43636</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43640</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>43644</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>43648</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>43648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>43648</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>43648</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>43653</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>43654</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>43656</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>43658</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>43665</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>43672</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>43676</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>43676</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>43684</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>43700</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>43713</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>43720</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>43725</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>43727</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>43732</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43733</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43738</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43738</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43740</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>43741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43742</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>43742</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>43746</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>43749</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>43753</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43754</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43766</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>43768</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>43770</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>43773</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43774</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43785</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43788</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43789</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43794</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43797</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43803</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43808</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43808</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43808</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43808</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43808</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43808</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43811</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43837</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43838</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43838</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43838</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>43844</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>43845</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>43845</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>43846</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43847</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43848</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43850</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43850</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43851</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43853</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43857</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43857</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43861</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43864</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43866</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43870</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43878</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43879</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43881</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43883</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43888</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43891</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43891</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43894</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>43895</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>43895</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>43896</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>43899</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>43899</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43899</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43901</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43905</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43906</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>43907</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>43907</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43910</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43913</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>43913</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>43913</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>43913</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>43913</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>43913</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>43913</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>43916</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>43916</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>43916</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>43920</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>43921</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>43922</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>43923</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>43923</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>43945</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>43945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>43956</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>43968</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>43978</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>43978</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>43983</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>43983</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>43997</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>43997</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44004</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44004</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44014</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44026</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44032</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44040</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44040</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44050</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44050</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44050</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44053</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44053</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44057</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44064</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44067</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44069</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44070</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44076</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44076</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44082</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44084</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44090</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44092</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44095</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44100</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44102</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44102</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44103</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44103</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44105</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44106</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44110</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44112</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44112</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44112</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44117</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44124</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44124</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44124</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44127</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44130</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44130</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44134</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44137</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44137</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44139</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44144</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44145</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44145</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44146</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44154</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44155</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44161</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44161</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44161</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44168</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>44175</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44183</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44189</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44193</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44193</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44193</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44204</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44206</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44207</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44208</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44209</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44211</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44216</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44217</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44218</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44221</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44221</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44221</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44221</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44221</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44221</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>44221</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44223</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44223</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44224</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44229</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44229</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44231</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44235</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44238</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44242</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44246</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44247</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44251</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44263</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44264</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44266</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44270</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44271</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44280</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44284</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44285</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44287</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44294</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44299</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>44301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44307</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44316</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44319</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44321</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44321</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44322</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44322</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44328</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44334</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44334</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>44340</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>44343</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44344</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44344</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44347</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44351</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44354</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>44358</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44362</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>44362</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44368</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44368</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44370</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44377</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44378</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44378</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44378</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44378</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44385</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44385</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44385</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>44385</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44385</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44386</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44389</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44389</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44389</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>44389</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>44389</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44389</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>44389</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>44392</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44392</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>44392</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44392</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44392</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44392</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44392</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44392</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44392</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44392</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44400</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>44403</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44404</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44412</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44417</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44418</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>44419</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44419</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44419</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44421</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>44423</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>44424</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44424</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>44425</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44431</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44434</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44434</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>44434</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>44435</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>44435</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44435</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44438</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44439</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44439</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44440</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44445</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>44446</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44448</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44448</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44448</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44449</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>44449</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>44450</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>44454</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44456</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44462</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44463</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44463</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44466</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44467</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44467</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44468</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44468</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44473</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44473</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>44475</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44480</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>44487</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44487</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>44487</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44488</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44488</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44489</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44490</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>44491</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44494</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44501</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>44505</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44505</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44508</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44509</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44509</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>44509</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44509</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44509</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44509</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44509</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44511</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>44512</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>44512</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44512</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44512</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44518</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44523</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44523</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44523</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44523</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44523</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44524</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44526</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44528</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44537</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44538</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>44538</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44543</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44546</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>44550</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44550</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44550</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44550</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44550</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44550</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44552</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44552</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>44552</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44557</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44564</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44564</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44564</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44564</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44564</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44572</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44574</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44580</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44580</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44580</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44580</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44581</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44581</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44581</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44582</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44582</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44587</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44596</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44602</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44602</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44603</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44606</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44607</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44607</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44607</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44608</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44608</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44610</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44615</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44616</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44616</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44620</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44623</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44624</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44627</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44627</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44629</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44629</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44629</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44629</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>44629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44634</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>44635</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>44641</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44641</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44643</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44644</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44649</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44649</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44655</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>44656</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44658</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44658</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44659</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44659</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44663</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44665</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44671</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>44671</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>44676</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>44678</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>44679</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44679</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44683</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>44686</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44698</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44699</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44709</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44711</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44719</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>44719</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44719</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44720</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>44734</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>44735</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44735</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44745</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44745</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44745</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44748</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44748</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44750</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44758</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44759</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44762</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44762</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44763</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44763</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44764</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44776</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44777</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44780</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44780</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44780</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44784</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44785</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>44787</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>44787</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44787</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>44787</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44787</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>44802</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>44806</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44806</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44810</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44812</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>44812</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44813</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44813</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44819</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>44819</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>44819</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>44820</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44820</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44820</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44823</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44823</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44823</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44824</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>44824</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>44825</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>44826</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44827</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44829</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44829</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44830</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44830</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44831</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44840</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44840</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44840</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>44846</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44846</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44846</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>44846</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>44846</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44852</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44853</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44853</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44854</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44858</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44861</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44861</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44862</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44864</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44866</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44867</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>44868</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>44868</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44868</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44662,7 +44662,7 @@
         <v>44872</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>44872</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>44875</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44876</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>44876</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>44876</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>44876</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>44879</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>44880</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>44880</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>44881</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>44881</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>44881</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>44881</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>44881</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44881</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44885</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>44886</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>44886</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44894</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>44894</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44894</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44895</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>44896</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44896</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44900</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>44900</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>44900</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>44900</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44909</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>44910</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>44910</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44911</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>44911</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>44916</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44916</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>44917</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44921</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>44924</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44929</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44936</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>44936</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44936</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44937</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>44938</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44938</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44943</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44943</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44943</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44943</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44945</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>44945</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44946</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44949</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>44950</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>44952</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44952</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>44952</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>44959</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>44960</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44970</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44973</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44976</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>44977</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>44977</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>44980</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44980</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44980</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>44980</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44982</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>44985</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>44988</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>44993</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>44993</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>44993</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>44994</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>44994</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44998</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44998</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44999</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>44999</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45000</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45005</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45005</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45006</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45009</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45012</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45012</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45012</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45012</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45013</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45015</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45021</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45025</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45029</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45029</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45033</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45033</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45033</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45033</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45033</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45035</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45037</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45040</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45040</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45040</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45040</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45040</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45041</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45041</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45041</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45044</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45050</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45050</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45050</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45056</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>45056</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45057</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>45058</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>45061</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45062</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45063</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45063</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45065</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45065</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45068</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45068</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45070</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45070</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45071</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45072</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45075</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45078</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45078</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45079</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45081</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45082</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45082</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45085</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45085</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45086</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45089</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45089</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45092</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45092</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45093</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45093</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45095</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45096</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45096</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45098</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>45098</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45098</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45098</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45098</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45099</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>45099</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45099</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45099</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45099</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45099</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45105</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45105</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45106</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45106</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45106</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45106</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>45106</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45107</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45107</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45107</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45107</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45107</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45113</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45113</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>45113</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>45113</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45113</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45113</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45119</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45119</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45120</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45120</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45123</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45127</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45127</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45133</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45137</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45138</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45140</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45141</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45146</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45146</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45146</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45147</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45147</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45148</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45149</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45149</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>45149</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>45154</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45156</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>45156</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45156</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45159</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>45161</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>45161</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45162</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56665,7 +56665,7 @@
         <v>45164</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45167</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45168</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         <v>45168</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45168</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>45169</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45170</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45170</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45170</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45170</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45170</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45171</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45171</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45173</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45173</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45173</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45173</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>45176</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45176</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45180</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45180</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45183</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45186</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45189</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45189</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45189</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45189</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58229,7 +58229,7 @@
         <v>45189</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45189</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45189</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>45189</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58457,7 +58457,7 @@
         <v>45189</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>45191</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45191</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>45191</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45191</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>45194</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45194</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>45194</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45194</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>45197</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45201</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45202</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         <v>45203</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>45203</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45203</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>45203</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45204</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>45204</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45205</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         <v>45208</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45208</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45210</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45211</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45211</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45212</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45215</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45221</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>45222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45222</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         <v>45222</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45222</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>45223</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>45223</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45226</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45229</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>45229</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45231</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -60623,7 +60623,7 @@
         <v>45233</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -60673,14 +60673,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 55274-2023</t>
+          <t>A 55223-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -60693,7 +60693,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>0.7</v>
+        <v>7.5</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -60730,14 +60730,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 55223-2023</t>
+          <t>A 55274-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>7.5</v>
+        <v>0.7</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -60787,14 +60787,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 56452-2023</t>
+          <t>A 56475-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -60844,14 +60844,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 56498-2023</t>
+          <t>A 56485-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -60901,14 +60901,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 56475-2023</t>
+          <t>A 56452-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -60921,7 +60921,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -60958,14 +60958,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 56485-2023</t>
+          <t>A 56498-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -61022,7 +61022,7 @@
         <v>45237</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61079,7 +61079,7 @@
         <v>45237</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61136,7 +61136,7 @@
         <v>45237</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61193,7 +61193,7 @@
         <v>45238</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61243,14 +61243,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 57176-2023</t>
+          <t>A 57153-2023</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>2.2</v>
+        <v>11.6</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -61300,14 +61300,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 57153-2023</t>
+          <t>A 57179-2023</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>11.6</v>
+        <v>2.3</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
     <row r="1048" ht="15" customHeight="1">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>A 57179-2023</t>
+          <t>A 57176-2023</t>
         </is>
       </c>
       <c r="B1048" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -61377,7 +61377,7 @@
         </is>
       </c>
       <c r="G1048" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -61421,7 +61421,7 @@
         <v>45242</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -61478,7 +61478,7 @@
         <v>45245</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -61533,14 +61533,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 57544-2023</t>
+          <t>A 57577-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -61553,7 +61553,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -61590,14 +61590,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 57577-2023</t>
+          <t>A 57544-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -61610,7 +61610,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -61654,7 +61654,7 @@
         <v>45249</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -61704,14 +61704,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 58602-2023</t>
+          <t>A 58653-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -61724,7 +61724,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -61761,14 +61761,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 58653-2023</t>
+          <t>A 58602-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -61781,7 +61781,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -61825,7 +61825,7 @@
         <v>45251</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -61887,7 +61887,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -61937,14 +61937,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 59312-2023</t>
+          <t>A 59203-2023</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -61957,7 +61957,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>8.699999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -61994,14 +61994,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59203-2023</t>
+          <t>A 59438-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>4.8</v>
+        <v>19.9</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -62051,14 +62051,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 59216-2023</t>
+          <t>A 59312-2023</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>2.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -62108,14 +62108,14 @@
     <row r="1061" ht="15" customHeight="1">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>A 59438-2023</t>
+          <t>A 59216-2023</t>
         </is>
       </c>
       <c r="B1061" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         </is>
       </c>
       <c r="G1061" t="n">
-        <v>19.9</v>
+        <v>2.1</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -62165,14 +62165,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 60019-2023</t>
+          <t>A 60018-2023</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62185,7 +62185,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -62222,14 +62222,14 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>A 60018-2023</t>
+          <t>A 60019-2023</t>
         </is>
       </c>
       <c r="B1063" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         </is>
       </c>
       <c r="G1063" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -564,7 +564,7 @@
         <v>43598</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>45203</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>43360</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44452</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45203</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>43382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43431</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43461</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43594</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>43882</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44043</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44148</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44221</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44446</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44450</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44589</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44755</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44762</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44805</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44813</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44886</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44894</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44938</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45016</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>43319</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>43319</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>43325</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>43327</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>43327</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>43332</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>43340</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>43341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>43346</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>43348</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>43349</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43350</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>43353</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>43353</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>43353</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>43360</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>43361</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>43362</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>43363</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43369</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>43370</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>43374</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43374</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>43374</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>43374</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>43382</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>43390</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>43390</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>43392</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>43392</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>43392</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>43392</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>43392</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>43392</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>43395</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>43397</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>43405</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>43405</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>43406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>43410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43416</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>43416</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>43416</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>43416</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>43416</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>43419</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43419</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>43419</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43431</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43437</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>43445</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>43453</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>43461</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>43461</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>43462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>43467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>43467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>43475</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>43476</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>43479</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>43479</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>43483</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>43485</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>43487</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>43490</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>43493</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>43494</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>43494</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>43494</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>43494</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>43494</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>43502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>43502</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>43507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>43507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>43515</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>43515</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>43524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>43528</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>43542</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43544</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43546</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43547</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>43547</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>43559</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>43560</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>43563</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>43566</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>43567</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>43570</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43570</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>43578</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>43581</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>43584</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>43584</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>43584</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43591</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>43594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>43594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>43594</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43594</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>43594</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43594</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43594</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43594</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43598</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>43598</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>43598</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>43598</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>43598</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>43605</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>43606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>43606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>43606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>43606</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>43607</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>43612</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>43615</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>43629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>43635</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>43636</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43640</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>43644</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>43648</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>43648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>43648</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>43648</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>43653</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>43654</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>43656</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>43658</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>43665</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>43672</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>43676</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>43676</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>43684</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>43700</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>43713</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>43720</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>43725</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>43727</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>43732</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43733</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43738</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43738</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43740</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>43741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43742</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>43742</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>43746</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>43749</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>43753</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43754</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43766</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>43768</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>43770</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>43773</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43774</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43785</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43788</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43789</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43794</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43797</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43803</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43808</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43808</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43808</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43808</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43808</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43808</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43811</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43837</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43838</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43838</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43838</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>43844</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>43845</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>43845</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>43846</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43847</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43848</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43850</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43850</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43851</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43853</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43857</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43857</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43861</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43864</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43866</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43870</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43878</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43879</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43881</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43883</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43888</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43891</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43891</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43894</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>43895</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>43895</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>43896</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>43899</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>43899</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43899</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43901</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43905</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43906</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>43907</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>43907</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43910</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43913</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>43913</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>43913</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>43913</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>43913</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>43913</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>43913</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>43916</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>43916</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>43916</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>43920</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>43921</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>43922</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>43923</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>43923</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>43945</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>43945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>43956</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>43968</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>43978</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>43978</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>43983</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>43983</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>43997</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>43997</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44004</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44004</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44014</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44026</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44032</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44040</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44040</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44050</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44050</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44050</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44053</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44053</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44057</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44064</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44067</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44069</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44070</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44076</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44076</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44082</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44084</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44090</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44092</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44095</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44100</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44102</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44102</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44103</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44103</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44105</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44106</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44110</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44112</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44112</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44112</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44117</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44124</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44124</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44124</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44127</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44130</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44130</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44134</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44137</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44137</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44139</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44144</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44145</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44145</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44146</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44154</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44155</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44161</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44161</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44161</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44168</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>44175</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44183</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44189</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44193</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44193</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44193</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44204</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44206</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44207</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44208</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44209</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44211</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44216</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44217</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44218</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44221</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44221</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44221</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44221</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44221</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44221</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>44221</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44223</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44223</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44224</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44229</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44229</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44231</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44235</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44238</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44242</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44246</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44247</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44251</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44263</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44264</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44266</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44270</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44271</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44280</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44284</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44285</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44287</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44294</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44299</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>44301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44307</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44316</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44319</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44321</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44321</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44322</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44322</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44328</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44334</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44334</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>44340</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>44343</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44344</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44344</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44347</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44351</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44354</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>44358</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44362</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>44362</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44368</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44368</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44370</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44377</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44378</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44378</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44378</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44378</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44385</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44385</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44385</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>44385</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44385</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44386</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44389</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44389</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44389</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>44389</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>44389</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44389</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>44389</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>44392</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44392</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>44392</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44392</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44392</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44392</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44392</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44392</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44392</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44392</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44400</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>44403</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44404</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44412</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44417</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44418</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>44419</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44419</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44419</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44421</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>44423</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>44424</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44424</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>44425</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44431</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44434</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44434</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>44434</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>44435</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>44435</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44435</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44438</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44439</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44439</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44440</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44445</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>44446</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44448</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44448</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44448</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44449</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>44449</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>44450</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>44454</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44456</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44462</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44463</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44463</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44466</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44467</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44467</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44468</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44468</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44473</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44473</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>44475</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44480</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>44487</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44487</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>44487</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44488</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44488</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44489</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44490</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>44491</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44494</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44501</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>44505</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44505</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44508</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44509</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44509</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>44509</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44509</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44509</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44509</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44509</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44511</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>44512</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>44512</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44512</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44512</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44518</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44523</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44523</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44523</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44523</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44523</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44524</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44526</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44528</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44537</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44538</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>44538</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44543</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44546</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>44550</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44550</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44550</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44550</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44550</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44550</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44552</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44552</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>44552</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44557</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44564</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44564</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44564</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44564</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44564</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44572</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44574</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44580</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44580</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44580</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44580</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44581</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44581</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44581</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44582</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44582</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44587</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44596</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44602</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44602</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44603</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44606</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44607</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44607</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44607</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44608</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44608</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44610</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44615</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44616</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44616</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44620</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44623</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44624</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44627</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44627</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44629</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44629</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44629</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44629</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>44629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44634</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>44635</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>44641</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44641</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44643</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44644</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44649</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44649</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44655</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>44656</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44658</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44658</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44659</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44659</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44663</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44665</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44671</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>44671</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>44676</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>44678</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>44679</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44679</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44683</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>44686</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44698</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44699</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44709</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44711</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44719</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>44719</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44719</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44720</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>44734</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>44735</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44735</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44745</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44745</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44745</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44748</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44748</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44750</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44758</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44759</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44762</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44762</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44763</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44763</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44764</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44776</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44777</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44780</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44780</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44780</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44784</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44785</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>44787</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>44787</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44787</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>44787</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44787</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>44802</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>44806</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44806</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44810</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44812</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>44812</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44813</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44813</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44819</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>44819</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>44819</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>44820</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44820</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44820</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44823</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44823</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44823</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44824</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>44824</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>44825</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>44826</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44827</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44829</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44829</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44830</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44830</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44831</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44840</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44840</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44840</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>44846</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44846</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44846</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>44846</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>44846</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44852</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44853</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44853</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44854</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44858</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44861</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44861</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44862</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44864</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44866</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44867</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>44868</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>44868</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44868</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44662,7 +44662,7 @@
         <v>44872</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>44872</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>44875</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44876</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>44876</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>44876</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>44876</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>44879</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>44880</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>44880</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>44881</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>44881</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>44881</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>44881</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>44881</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44881</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44885</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>44886</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>44886</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44894</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>44894</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44894</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44895</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>44896</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44896</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44900</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>44900</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>44900</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>44900</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44909</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>44910</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>44910</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44911</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>44911</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>44916</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44916</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>44917</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44921</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>44924</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44929</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44936</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>44936</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44936</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44937</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>44938</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44938</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44943</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44943</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44943</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44943</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44945</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>44945</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44946</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44949</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>44950</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>44952</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44952</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>44952</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>44959</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>44960</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44970</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44973</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44976</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>44977</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>44977</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>44980</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44980</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44980</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>44980</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44982</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>44985</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>44988</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>44993</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>44993</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>44993</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>44994</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>44994</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44998</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44998</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44999</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>44999</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45000</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45005</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45005</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45006</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45009</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45012</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45012</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45012</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45012</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45013</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45015</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45021</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45025</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45029</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45029</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45033</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45033</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45033</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45033</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45033</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45035</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45037</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45040</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45040</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45040</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45040</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45040</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45041</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45041</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45041</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45044</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45050</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45050</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45050</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45056</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>45056</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45057</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>45058</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>45061</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45062</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45063</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45063</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45065</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45065</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45068</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45068</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45070</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45070</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45071</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45072</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45075</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45078</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45078</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45079</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45081</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45082</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45082</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45085</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45085</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45086</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45089</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45089</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45092</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45092</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45093</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45093</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45095</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45096</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45096</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45098</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>45098</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45098</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45098</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45098</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45099</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>45099</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45099</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45099</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45099</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45099</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45105</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45105</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45106</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45106</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45106</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45106</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>45106</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45107</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45107</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45107</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45107</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45107</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45113</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45113</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>45113</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>45113</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45113</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45113</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45119</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45119</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45120</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45120</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45123</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45127</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45127</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45133</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45137</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45138</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45140</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45141</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45146</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45146</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45146</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45147</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45147</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45148</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45149</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45149</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>45149</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>45154</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45156</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>45156</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45156</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45159</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>45161</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>45161</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45162</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56665,7 +56665,7 @@
         <v>45164</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45167</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45168</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         <v>45168</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45168</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>45169</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45170</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45170</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45170</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45170</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45170</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45171</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45171</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45173</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45173</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45173</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45173</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>45176</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45176</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45180</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45180</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45183</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45186</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45189</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45189</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45189</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45189</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58229,7 +58229,7 @@
         <v>45189</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45189</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45189</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>45189</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58457,7 +58457,7 @@
         <v>45189</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>45191</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45191</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>45191</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45191</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>45194</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45194</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>45194</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45194</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>45197</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45201</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45202</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         <v>45203</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>45203</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45203</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>45203</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45204</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>45204</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45205</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         <v>45208</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45208</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45210</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45211</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45211</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45212</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45215</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45221</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>45222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45222</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         <v>45222</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45222</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>45223</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>45223</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45226</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45229</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>45229</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45231</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -60623,7 +60623,7 @@
         <v>45233</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>45237</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -60730,14 +60730,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 55274-2023</t>
+          <t>A 56475-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -60787,14 +60787,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 56475-2023</t>
+          <t>A 56485-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -60844,14 +60844,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 56485-2023</t>
+          <t>A 56506-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -60908,7 +60908,7 @@
         <v>45237</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -60965,7 +60965,7 @@
         <v>45237</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -61015,14 +61015,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 56479-2023</t>
+          <t>A 55274-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61035,7 +61035,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -61072,14 +61072,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 56489-2023</t>
+          <t>A 56479-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61092,7 +61092,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -61129,14 +61129,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 56506-2023</t>
+          <t>A 56489-2023</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -61193,7 +61193,7 @@
         <v>45238</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61243,14 +61243,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 57153-2023</t>
+          <t>A 57176-2023</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>11.6</v>
+        <v>2.2</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -61300,14 +61300,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 57179-2023</t>
+          <t>A 57153-2023</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>2.3</v>
+        <v>11.6</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
     <row r="1048" ht="15" customHeight="1">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>A 57176-2023</t>
+          <t>A 57179-2023</t>
         </is>
       </c>
       <c r="B1048" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -61377,7 +61377,7 @@
         </is>
       </c>
       <c r="G1048" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -61421,7 +61421,7 @@
         <v>45242</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -61478,7 +61478,7 @@
         <v>45245</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -61533,14 +61533,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 57577-2023</t>
+          <t>A 57544-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -61553,7 +61553,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -61590,14 +61590,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 57544-2023</t>
+          <t>A 57577-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -61610,7 +61610,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -61654,7 +61654,7 @@
         <v>45249</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -61704,14 +61704,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 58653-2023</t>
+          <t>A 58602-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -61724,7 +61724,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -61761,14 +61761,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 58602-2023</t>
+          <t>A 58646-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -61780,8 +61780,13 @@
           <t>SÄFFLE</t>
         </is>
       </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G1055" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -61818,14 +61823,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 58646-2023</t>
+          <t>A 58653-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -61837,13 +61842,8 @@
           <t>SÄFFLE</t>
         </is>
       </c>
-      <c r="F1056" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G1056" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -61887,7 +61887,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -61937,14 +61937,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 59203-2023</t>
+          <t>A 59438-2023</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -61957,7 +61957,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>4.8</v>
+        <v>19.9</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -61994,14 +61994,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59438-2023</t>
+          <t>A 59312-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>19.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -62051,14 +62051,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 59312-2023</t>
+          <t>A 59203-2023</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>8.699999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -62115,7 +62115,7 @@
         <v>45253</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>45258</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45258</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -564,7 +564,7 @@
         <v>43598</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>45203</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>43360</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44452</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45203</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>43382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43431</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43461</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43594</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>43882</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44043</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44148</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44221</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44446</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44450</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44589</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44755</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44762</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44805</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44813</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44886</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44894</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44938</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45016</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>43319</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>43319</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>43325</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>43327</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>43327</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>43332</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>43340</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>43341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>43346</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>43348</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>43349</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43350</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>43353</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>43353</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>43353</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>43360</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>43361</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>43362</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>43363</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43369</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>43370</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>43374</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43374</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>43374</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>43374</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>43382</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>43390</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>43390</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>43392</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>43392</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>43392</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>43392</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>43392</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>43392</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>43395</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>43397</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>43405</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>43405</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>43406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>43410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43416</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>43416</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>43416</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>43416</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>43416</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>43419</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43419</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>43419</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43431</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43437</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>43445</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>43453</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>43461</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>43461</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>43462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>43467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>43467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>43475</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>43476</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>43479</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>43479</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>43483</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>43485</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>43487</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>43490</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>43493</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>43494</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>43494</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>43494</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>43494</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>43494</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>43502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>43502</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>43507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>43507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>43515</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>43515</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>43524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>43528</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>43542</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43544</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43546</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43547</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>43547</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>43559</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>43560</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>43563</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>43566</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>43567</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>43570</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43570</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>43578</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>43581</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>43584</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>43584</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>43584</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43591</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>43594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>43594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>43594</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43594</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>43594</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43594</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43594</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43594</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43598</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>43598</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>43598</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>43598</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>43598</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>43605</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>43606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>43606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>43606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>43606</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>43607</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>43612</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>43615</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>43629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>43635</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>43636</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43640</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>43644</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>43648</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>43648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>43648</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>43648</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>43653</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>43654</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>43656</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>43658</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>43665</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>43672</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>43676</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>43676</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>43684</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>43700</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>43713</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>43720</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>43725</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>43727</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>43732</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43733</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43738</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43738</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43740</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>43741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43742</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>43742</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>43746</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>43749</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>43753</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43754</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43766</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>43768</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>43770</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>43773</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43774</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43785</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43788</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43789</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43794</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43797</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43803</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43808</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43808</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43808</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43808</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43808</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43808</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43811</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43837</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43838</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43838</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43838</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>43844</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>43845</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>43845</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>43846</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43847</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43848</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43850</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43850</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43851</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43853</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43857</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43857</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43861</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43864</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43866</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43870</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43878</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43879</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43881</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43883</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43888</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43891</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43891</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43894</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>43895</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>43895</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>43896</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>43899</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>43899</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43899</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43901</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43905</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43906</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>43907</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>43907</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43910</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43913</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>43913</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>43913</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>43913</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>43913</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>43913</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>43913</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>43916</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>43916</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>43916</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>43920</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>43921</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>43922</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>43923</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>43923</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>43945</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>43945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>43956</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>43968</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>43978</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>43978</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>43983</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>43983</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>43997</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>43997</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44004</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44004</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44014</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44026</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44032</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44040</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44040</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44050</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44050</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44050</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44053</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44053</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44057</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44064</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44067</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44069</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44070</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44076</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44076</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44082</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44084</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44090</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44092</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44095</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44100</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44102</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44102</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44103</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44103</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44105</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44106</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44110</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44112</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44112</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44112</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44117</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44124</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44124</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44124</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44127</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44130</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44130</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44134</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44137</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44137</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44139</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44144</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44145</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44145</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44146</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44154</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44155</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44161</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44161</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44161</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44168</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>44175</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44183</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44189</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44193</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44193</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44193</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44204</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44206</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44207</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44208</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44209</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44211</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44216</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44217</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44218</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44221</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44221</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44221</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44221</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44221</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44221</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>44221</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44223</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44223</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44224</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44229</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44229</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44231</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44235</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44238</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44242</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44246</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44247</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44251</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44263</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44264</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44266</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44270</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44271</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44280</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44284</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44285</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44287</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44294</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44299</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>44301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44307</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44316</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44319</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44321</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44321</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44322</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44322</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44328</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44334</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44334</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>44340</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>44343</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44344</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44344</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44347</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44351</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44354</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>44358</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44362</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>44362</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44368</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44368</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44370</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44377</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44378</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44378</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44378</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44378</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44385</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44385</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44385</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>44385</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44385</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44386</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44389</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44389</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44389</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>44389</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>44389</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44389</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>44389</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>44392</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44392</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>44392</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44392</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44392</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44392</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44392</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44392</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44392</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44392</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44400</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>44403</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44404</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44412</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44417</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44418</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>44419</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44419</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44419</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44421</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>44423</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>44424</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44424</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>44425</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44431</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44434</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44434</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>44434</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>44435</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>44435</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44435</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44438</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44439</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44439</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44440</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44445</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>44446</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44448</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44448</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44448</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44449</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>44449</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>44450</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>44454</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44456</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44462</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44463</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44463</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44466</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44467</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44467</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44468</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44468</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44473</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44473</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>44475</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44480</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>44487</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44487</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>44487</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44488</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44488</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44489</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44490</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>44491</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44494</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44501</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>44505</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44505</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44508</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44509</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44509</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>44509</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44509</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44509</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44509</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44509</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44511</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>44512</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>44512</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44512</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44512</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44518</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44523</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44523</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44523</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44523</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44523</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44524</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44526</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44528</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44537</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44538</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>44538</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44543</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44546</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>44550</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44550</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44550</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44550</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44550</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44550</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44552</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44552</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>44552</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44557</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44564</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44564</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44564</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44564</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44564</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44572</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44574</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44580</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44580</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44580</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44580</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44581</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44581</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44581</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44582</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44582</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44587</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44596</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44602</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44602</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44603</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44606</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44607</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44607</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44607</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44608</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44608</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44610</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44615</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44616</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44616</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44620</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44623</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44624</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44627</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44627</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44629</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44629</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44629</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44629</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>44629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44634</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>44635</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>44641</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44641</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44643</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44644</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44649</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44649</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44655</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>44656</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44658</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44658</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44659</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44659</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44663</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44665</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44671</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>44671</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>44676</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>44678</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>44679</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44679</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44683</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>44686</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44698</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44699</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44709</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44711</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44719</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>44719</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44719</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44720</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>44734</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>44735</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44735</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44745</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44745</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44745</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44748</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44748</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44750</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44758</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44759</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44762</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44762</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44763</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44763</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44764</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44776</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44777</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44780</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44780</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44780</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44784</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44785</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>44787</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>44787</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44787</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>44787</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44787</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>44802</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>44806</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44806</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44810</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44812</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>44812</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44813</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44813</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44819</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>44819</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>44819</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>44820</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44820</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44820</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44823</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44823</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44823</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44824</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>44824</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>44825</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>44826</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44827</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44829</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44829</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44830</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44830</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44831</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44840</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44840</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44840</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>44846</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44846</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44846</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>44846</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>44846</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44852</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44853</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44853</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44854</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44858</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44861</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44861</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44862</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44864</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44866</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44867</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>44868</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>44868</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44868</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44662,7 +44662,7 @@
         <v>44872</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>44872</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>44875</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44876</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>44876</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>44876</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>44876</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>44879</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>44880</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>44880</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>44881</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>44881</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>44881</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>44881</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>44881</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44881</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44885</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>44886</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>44886</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44894</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>44894</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44894</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44895</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>44896</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44896</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44900</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>44900</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>44900</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>44900</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44909</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>44910</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>44910</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44911</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>44911</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>44916</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44916</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>44917</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44921</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>44924</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44929</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44936</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>44936</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44936</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44937</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>44938</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44938</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44943</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44943</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44943</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44943</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44945</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>44945</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44946</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44949</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>44950</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>44952</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44952</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>44952</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>44959</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>44960</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44970</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44973</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44976</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>44977</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>44977</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>44980</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44980</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44980</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>44980</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44982</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>44985</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>44988</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>44993</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>44993</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>44993</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>44994</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>44994</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44998</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44998</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44999</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>44999</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45000</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45005</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45005</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45006</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45009</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45012</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45012</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45012</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45012</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45013</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45015</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45021</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45025</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45029</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45029</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45033</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45033</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45033</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45033</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45033</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45035</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45037</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45040</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45040</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45040</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45040</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45040</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45041</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45041</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45041</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45044</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45050</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45050</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45050</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45056</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>45056</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45057</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>45058</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>45061</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45062</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45063</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45063</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45065</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45065</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45068</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45068</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45070</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45070</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45071</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45072</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45075</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45078</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45078</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45079</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45081</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45082</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45082</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45085</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45085</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45086</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45089</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45089</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45092</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45092</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45093</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45093</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45095</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45096</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45096</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45098</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>45098</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45098</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45098</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45098</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45099</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>45099</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45099</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45099</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45099</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45099</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45105</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45105</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45106</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45106</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45106</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45106</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>45106</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45107</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45107</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45107</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45107</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45107</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45113</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45113</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>45113</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>45113</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45113</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45113</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45119</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45119</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45120</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45120</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45123</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45127</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45127</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45133</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45137</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45138</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45140</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45141</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45146</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45146</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45146</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45147</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45147</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45148</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45149</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45149</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>45149</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>45154</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45156</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>45156</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45156</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45159</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>45161</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>45161</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45162</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56665,7 +56665,7 @@
         <v>45164</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45167</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45168</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         <v>45168</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45168</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>45169</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45170</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45170</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45170</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45170</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45170</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45171</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45171</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45173</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45173</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45173</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45173</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>45176</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45176</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45180</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45180</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45183</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45186</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45189</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45189</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45189</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45189</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58229,7 +58229,7 @@
         <v>45189</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45189</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45189</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>45189</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58457,7 +58457,7 @@
         <v>45189</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>45191</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45191</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>45191</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45191</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>45194</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45194</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>45194</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45194</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>45197</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45201</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45202</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         <v>45203</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>45203</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45203</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>45203</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45204</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>45204</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45205</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         <v>45208</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45208</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45210</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45211</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45211</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45212</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45215</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45221</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>45222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45222</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         <v>45222</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45222</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>45223</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>45223</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45226</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45229</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>45229</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45231</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -60623,7 +60623,7 @@
         <v>45233</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>45237</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -60730,14 +60730,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 56475-2023</t>
+          <t>A 55274-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -60787,14 +60787,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 56485-2023</t>
+          <t>A 56479-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -60844,14 +60844,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 56506-2023</t>
+          <t>A 56475-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -60901,14 +60901,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 56452-2023</t>
+          <t>A 56485-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -60921,7 +60921,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>7.1</v>
+        <v>1</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -60958,14 +60958,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 56498-2023</t>
+          <t>A 56452-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -61015,14 +61015,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 55274-2023</t>
+          <t>A 56498-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61035,7 +61035,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -61072,14 +61072,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 56479-2023</t>
+          <t>A 56506-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61092,7 +61092,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -61136,7 +61136,7 @@
         <v>45237</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61193,7 +61193,7 @@
         <v>45238</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>45239</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -61307,7 +61307,7 @@
         <v>45239</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45239</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>45242</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -61478,7 +61478,7 @@
         <v>45245</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -61540,7 +61540,7 @@
         <v>45246</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -61597,7 +61597,7 @@
         <v>45246</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -61654,7 +61654,7 @@
         <v>45249</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>45251</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -61761,14 +61761,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 58646-2023</t>
+          <t>A 58653-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -61780,13 +61780,8 @@
           <t>SÄFFLE</t>
         </is>
       </c>
-      <c r="F1055" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G1055" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -61823,14 +61818,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 58653-2023</t>
+          <t>A 58646-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -61842,8 +61837,13 @@
           <t>SÄFFLE</t>
         </is>
       </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G1056" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -61887,7 +61887,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -61937,14 +61937,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 59438-2023</t>
+          <t>A 59312-2023</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -61957,7 +61957,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>19.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -61994,14 +61994,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59312-2023</t>
+          <t>A 59438-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>8.699999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -62058,7 +62058,7 @@
         <v>45253</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62115,7 +62115,7 @@
         <v>45253</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>45258</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45258</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1063"/>
+  <dimension ref="A1:Y1064"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43598</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>45203</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>43360</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44452</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45203</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>43382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43431</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43461</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43594</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>43882</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44043</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44148</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44221</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44446</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44450</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44589</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44755</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44762</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44805</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44813</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44886</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44894</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44938</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45016</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>43319</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>43319</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>43325</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>43327</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>43327</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>43332</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>43340</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>43341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>43346</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>43348</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>43349</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43350</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>43353</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>43353</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>43353</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>43360</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>43361</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>43362</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>43363</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43369</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>43370</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>43374</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43374</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>43374</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>43374</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>43382</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>43390</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>43390</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>43392</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>43392</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>43392</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>43392</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>43392</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>43392</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>43395</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>43397</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>43405</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>43405</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>43406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>43410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43416</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>43416</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>43416</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>43416</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>43416</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>43419</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43419</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>43419</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43431</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43437</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>43445</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>43453</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>43461</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>43461</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>43462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>43467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>43467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>43475</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>43476</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>43479</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>43479</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>43483</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>43485</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>43487</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>43490</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>43493</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>43494</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>43494</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>43494</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>43494</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>43494</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>43502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>43502</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>43507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>43507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>43515</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>43515</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>43524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>43528</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>43542</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43544</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43546</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43547</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>43547</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>43559</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>43560</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>43563</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>43566</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>43567</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>43570</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43570</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>43578</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>43581</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>43584</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>43584</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>43584</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43591</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>43594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>43594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>43594</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43594</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>43594</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43594</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43594</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43594</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43598</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>43598</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>43598</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>43598</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>43598</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>43605</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>43606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>43606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>43606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>43606</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>43607</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>43612</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>43615</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>43629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>43635</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>43636</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43640</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>43644</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>43648</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>43648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>43648</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>43648</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>43653</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>43654</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>43656</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>43658</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>43665</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>43672</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>43676</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>43676</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>43684</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>43700</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>43713</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>43720</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>43725</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>43727</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>43732</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43733</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43738</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43738</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43740</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>43741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43742</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>43742</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>43746</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>43749</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>43753</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43754</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43766</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>43768</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>43770</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>43773</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43774</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43785</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43788</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43789</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43794</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43797</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43803</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43808</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43808</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43808</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43808</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43808</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43808</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43811</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43837</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43838</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43838</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43838</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>43844</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>43845</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>43845</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>43846</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43847</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43848</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43850</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43850</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43851</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43853</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43857</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43857</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43861</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43864</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43866</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43870</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43878</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43879</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43881</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43883</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43888</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43891</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43891</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43894</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>43895</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>43895</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>43896</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>43899</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>43899</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43899</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43901</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43905</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43906</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>43907</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>43907</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43910</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43913</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>43913</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>43913</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>43913</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>43913</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>43913</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>43913</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>43916</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>43916</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>43916</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>43920</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>43921</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>43922</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>43923</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>43923</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>43945</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>43945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>43956</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>43968</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>43978</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>43978</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>43983</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>43983</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>43997</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>43997</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44004</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44004</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44014</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44026</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44032</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44040</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44040</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44050</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44050</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44050</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44053</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44053</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44057</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44064</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44067</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44069</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44070</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44076</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44076</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44082</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44084</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44090</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44092</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44095</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44100</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44102</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44102</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44103</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44103</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44105</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44106</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44110</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44112</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44112</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44112</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44117</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44124</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44124</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44124</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44127</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44130</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44130</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44134</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44137</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44137</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44139</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44144</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44145</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44145</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44146</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44154</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44155</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44161</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44161</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44161</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44168</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>44175</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44183</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44189</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44193</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44193</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44193</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44204</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44206</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44207</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44208</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44209</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44211</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44216</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44217</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44218</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44221</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44221</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44221</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44221</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44221</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44221</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>44221</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44223</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44223</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44224</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44229</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44229</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44231</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44235</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44238</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44242</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44246</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44247</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44251</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44263</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44264</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44266</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44270</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44271</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44280</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44284</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44285</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44287</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44294</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44299</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>44301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44307</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44316</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44319</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44321</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44321</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44322</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44322</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44328</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44334</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44334</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>44340</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>44343</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44344</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44344</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44347</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44351</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44354</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>44358</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44362</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>44362</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44368</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44368</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44370</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44377</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44378</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44378</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44378</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44378</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44385</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44385</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44385</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>44385</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44385</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44386</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44389</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44389</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44389</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>44389</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>44389</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44389</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>44389</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>44392</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44392</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>44392</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44392</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44392</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44392</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44392</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44392</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44392</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44392</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44400</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>44403</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44404</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44412</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44417</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44418</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>44419</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44419</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44419</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44421</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>44423</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>44424</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44424</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>44425</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44431</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44434</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44434</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>44434</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>44435</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>44435</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44435</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44438</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44439</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44439</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44440</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44445</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>44446</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44448</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44448</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44448</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44449</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>44449</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>44450</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>44454</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44456</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44462</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44463</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44463</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44466</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44467</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44467</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44468</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44468</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44473</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44473</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>44475</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44480</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>44487</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44487</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>44487</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44488</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44488</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44489</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44490</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>44491</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44494</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44501</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>44505</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44505</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44508</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44509</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44509</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>44509</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44509</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44509</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44509</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44509</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44511</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>44512</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>44512</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44512</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44512</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44518</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44523</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44523</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44523</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44523</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44523</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44524</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44526</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44528</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44537</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44538</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>44538</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44543</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44546</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>44550</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44550</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44550</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44550</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44550</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44550</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44552</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44552</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>44552</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44557</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44564</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44564</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44564</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44564</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44564</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44572</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44574</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44580</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44580</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44580</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44580</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44581</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44581</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44581</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44582</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44582</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44587</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44596</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44602</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44602</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44603</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44606</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44607</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44607</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44607</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44608</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44608</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44610</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44615</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44616</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44616</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44620</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44623</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44624</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44627</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44627</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44629</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44629</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44629</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44629</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>44629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44634</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>44635</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>44641</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44641</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44643</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44644</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44649</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44649</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44655</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>44656</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44658</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44658</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44659</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44659</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44663</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44665</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44671</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>44671</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>44676</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>44678</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>44679</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44679</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44683</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>44686</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44698</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44699</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44709</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44711</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44719</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>44719</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44719</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44720</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>44734</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>44735</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44735</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44745</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44745</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44745</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44748</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44748</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44750</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44758</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44759</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44762</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44762</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44763</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44763</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44764</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44776</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44777</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44780</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44780</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44780</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44784</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44785</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>44787</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>44787</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44787</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>44787</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44787</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>44802</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>44806</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44806</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44810</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44812</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>44812</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44813</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44813</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44819</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>44819</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>44819</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>44820</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44820</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44820</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44823</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44823</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44823</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44824</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>44824</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>44825</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>44826</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44827</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44829</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44829</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44830</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44830</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44831</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44840</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44840</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44840</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>44846</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44846</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44846</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>44846</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>44846</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44852</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44853</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44853</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44854</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44858</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44861</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44861</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44862</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44864</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44866</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44867</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>44868</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>44868</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44868</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44662,7 +44662,7 @@
         <v>44872</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>44872</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>44875</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44876</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>44876</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>44876</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>44876</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>44879</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>44880</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>44880</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>44881</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>44881</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>44881</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>44881</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>44881</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44881</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44885</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>44886</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>44886</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44894</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>44894</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44894</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44895</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>44896</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44896</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44900</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>44900</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>44900</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>44900</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44909</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>44910</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>44910</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44911</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>44911</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>44916</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44916</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>44917</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44921</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>44924</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44929</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44936</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>44936</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44936</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44937</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>44938</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44938</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44943</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44943</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44943</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44943</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44945</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>44945</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44946</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44949</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>44950</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>44952</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44952</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>44952</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>44959</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>44960</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44970</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44973</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44976</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>44977</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>44977</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>44980</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44980</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44980</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>44980</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44982</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>44985</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>44988</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>44993</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>44993</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>44993</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>44994</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>44994</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44998</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44998</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44999</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>44999</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45000</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45005</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45005</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45006</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45009</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45012</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45012</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45012</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45012</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45013</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45015</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45021</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45025</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45029</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45029</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45033</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45033</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45033</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45033</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45033</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45035</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45037</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45040</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45040</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45040</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45040</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45040</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45041</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45041</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45041</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45044</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45050</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45050</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45050</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45056</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>45056</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45057</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>45058</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>45061</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45062</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45063</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45063</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45065</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45065</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45068</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45068</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45070</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45070</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45071</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45072</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45075</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45078</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45078</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45079</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45081</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45082</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45082</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45085</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45085</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45086</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45089</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45089</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45092</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45092</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45093</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45093</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45095</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45096</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45096</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45098</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>45098</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45098</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45098</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45098</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45099</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>45099</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45099</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45099</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45099</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45099</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45105</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45105</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45106</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45106</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45106</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45106</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>45106</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45107</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45107</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45107</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45107</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45107</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45113</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45113</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>45113</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>45113</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45113</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45113</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45119</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45119</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45120</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45120</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45123</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45127</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45127</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45133</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45137</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45138</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45140</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45141</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45146</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45146</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45146</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45147</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45147</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45148</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45149</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45149</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>45149</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>45154</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45156</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>45156</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45156</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45159</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>45161</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>45161</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45162</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56665,7 +56665,7 @@
         <v>45164</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45167</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45168</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         <v>45168</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45168</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>45169</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45170</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45170</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45170</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45170</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45170</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45171</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45171</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45173</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45173</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45173</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45173</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>45176</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45176</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45180</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45180</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45183</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45186</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45189</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45189</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45189</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45189</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58229,7 +58229,7 @@
         <v>45189</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45189</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45189</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>45189</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58457,7 +58457,7 @@
         <v>45189</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>45191</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45191</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>45191</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45191</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>45194</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45194</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>45194</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45194</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>45197</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45201</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45202</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         <v>45203</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>45203</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45203</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>45203</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45204</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>45204</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45205</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         <v>45208</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45208</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45210</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45211</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45211</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45212</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45215</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45221</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>45222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45222</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         <v>45222</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45222</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>45223</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>45223</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45226</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45229</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>45229</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45231</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -60623,7 +60623,7 @@
         <v>45233</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -60673,14 +60673,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 55223-2023</t>
+          <t>A 56452-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -60693,7 +60693,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -60737,7 +60737,7 @@
         <v>45237</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -60787,14 +60787,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 56479-2023</t>
+          <t>A 56475-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -60844,14 +60844,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 56475-2023</t>
+          <t>A 55223-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -60901,14 +60901,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 56485-2023</t>
+          <t>A 56506-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -60921,7 +60921,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -60958,14 +60958,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 56452-2023</t>
+          <t>A 56479-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>7.1</v>
+        <v>3.2</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -61015,14 +61015,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 56498-2023</t>
+          <t>A 56489-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61035,7 +61035,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -61072,14 +61072,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 56506-2023</t>
+          <t>A 56498-2023</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61092,7 +61092,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -61129,14 +61129,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 56489-2023</t>
+          <t>A 56485-2023</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -61193,7 +61193,7 @@
         <v>45238</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61243,14 +61243,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 57176-2023</t>
+          <t>A 57153-2023</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>2.2</v>
+        <v>11.6</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -61300,14 +61300,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 57153-2023</t>
+          <t>A 57176-2023</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>11.6</v>
+        <v>2.2</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>45239</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>45242</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -61478,7 +61478,7 @@
         <v>45245</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -61540,7 +61540,7 @@
         <v>45246</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -61597,7 +61597,7 @@
         <v>45246</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -61654,7 +61654,7 @@
         <v>45249</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>45251</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -61761,14 +61761,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 58653-2023</t>
+          <t>A 58646-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -61780,8 +61780,13 @@
           <t>SÄFFLE</t>
         </is>
       </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G1055" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -61818,14 +61823,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 58646-2023</t>
+          <t>A 58653-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -61837,13 +61842,8 @@
           <t>SÄFFLE</t>
         </is>
       </c>
-      <c r="F1056" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G1056" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -61887,7 +61887,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -61944,7 +61944,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -61994,14 +61994,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59438-2023</t>
+          <t>A 59203-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>19.9</v>
+        <v>4.8</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -62051,14 +62051,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 59203-2023</t>
+          <t>A 59216-2023</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -62108,14 +62108,14 @@
     <row r="1061" ht="15" customHeight="1">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>A 59216-2023</t>
+          <t>A 59438-2023</t>
         </is>
       </c>
       <c r="B1061" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         </is>
       </c>
       <c r="G1061" t="n">
-        <v>2.1</v>
+        <v>19.9</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -62172,7 +62172,7 @@
         <v>45258</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
       </c>
       <c r="R1062" s="2" t="inlineStr"/>
     </row>
-    <row r="1063">
+    <row r="1063" ht="15" customHeight="1">
       <c r="A1063" t="inlineStr">
         <is>
           <t>A 60019-2023</t>
@@ -62229,7 +62229,7 @@
         <v>45258</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -62275,6 +62275,63 @@
         <v>0</v>
       </c>
       <c r="R1063" s="2" t="inlineStr"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>A 61223-2023</t>
+        </is>
+      </c>
+      <c r="B1064" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C1064" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>SÄFFLE</t>
+        </is>
+      </c>
+      <c r="G1064" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1064" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1064"/>
+  <dimension ref="A1:Y1065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43598</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>45203</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>43360</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44452</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45203</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>43382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43431</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43461</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43594</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>43882</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44043</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44148</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44221</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44446</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44450</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44589</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44755</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44762</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44805</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44813</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44886</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44894</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44938</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45016</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>43319</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>43319</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>43325</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>43327</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>43327</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>43332</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>43340</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>43341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>43346</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>43348</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>43349</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43350</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>43353</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>43353</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>43353</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>43360</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>43361</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>43362</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>43363</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43369</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>43370</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>43374</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43374</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>43374</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>43374</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>43382</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>43390</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>43390</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>43392</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>43392</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>43392</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>43392</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>43392</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>43392</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>43395</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>43397</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>43405</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>43405</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>43406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>43410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43416</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>43416</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>43416</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>43416</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>43416</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>43419</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43419</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>43419</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43431</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43437</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>43445</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>43453</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>43461</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>43461</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>43462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>43467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>43467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>43475</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>43476</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>43479</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>43479</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>43483</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>43485</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>43487</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>43490</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>43493</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>43494</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>43494</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>43494</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>43494</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>43494</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>43502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>43502</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>43507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>43507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>43515</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>43515</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>43524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>43528</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>43542</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43544</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43546</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43547</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>43547</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>43559</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>43560</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>43563</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>43566</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>43567</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>43570</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43570</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>43578</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>43581</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>43584</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>43584</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>43584</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43591</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>43594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>43594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>43594</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43594</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>43594</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43594</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43594</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43594</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43598</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>43598</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>43598</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>43598</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>43598</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>43605</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>43606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>43606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>43606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>43606</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>43607</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>43612</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>43615</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>43629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>43635</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>43636</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43640</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>43644</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>43648</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>43648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>43648</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>43648</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>43653</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>43654</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>43656</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>43658</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>43665</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>43672</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>43676</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>43676</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>43684</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>43700</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>43713</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>43720</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>43725</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>43727</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>43732</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43733</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43738</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43738</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43740</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>43741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43742</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>43742</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>43746</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>43749</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>43753</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43754</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43766</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>43768</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>43770</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>43773</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43774</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43785</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43788</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43789</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43794</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43797</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43803</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43808</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43808</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43808</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43808</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43808</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43808</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43811</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43837</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43838</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43838</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43838</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>43844</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>43845</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>43845</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>43846</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43847</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43848</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43850</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43850</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43851</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43853</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43857</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43857</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43861</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43864</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43866</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43870</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43878</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43879</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43881</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43883</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43888</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43891</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43891</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43894</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>43895</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>43895</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>43896</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>43899</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>43899</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43899</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43901</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43905</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43906</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>43907</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>43907</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43910</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43913</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>43913</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>43913</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>43913</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>43913</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>43913</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>43913</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>43916</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>43916</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>43916</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>43920</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>43921</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>43922</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>43923</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>43923</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>43945</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>43945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>43956</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>43968</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>43978</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>43978</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>43983</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>43983</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>43997</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>43997</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44004</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44004</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44014</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44026</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44032</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44040</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44040</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44050</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44050</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44050</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44053</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44053</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44057</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44064</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44067</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44069</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44070</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44076</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44076</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44082</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44084</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44090</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44092</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44095</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44100</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44102</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44102</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44103</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44103</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44105</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44106</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44110</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44112</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44112</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44112</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44117</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44124</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44124</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44124</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44127</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44130</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44130</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44134</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44137</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44137</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44139</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44144</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44145</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44145</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44146</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44154</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44155</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44161</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44161</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44161</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44168</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>44175</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44183</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44189</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44193</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44193</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44193</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44204</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44206</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44207</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44208</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44209</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44211</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44216</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44217</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44218</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44221</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44221</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44221</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44221</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44221</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44221</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>44221</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44223</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44223</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44224</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44229</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44229</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44231</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44235</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44238</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44242</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44246</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44247</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44251</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44263</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44264</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44266</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44270</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44271</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44280</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44284</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44285</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44287</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44294</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44299</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>44301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44307</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44316</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44319</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44321</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44321</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44322</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44322</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44328</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44334</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44334</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>44340</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>44343</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44344</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44344</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44347</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44351</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44354</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>44358</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44362</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>44362</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44368</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44368</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44370</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44377</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44378</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44378</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44378</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44378</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44385</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44385</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44385</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>44385</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44385</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44386</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44389</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44389</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44389</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>44389</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>44389</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44389</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>44389</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>44392</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44392</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>44392</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44392</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44392</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44392</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44392</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44392</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44392</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44392</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44400</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>44403</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44404</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44412</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44417</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44418</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>44419</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44419</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44419</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44421</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>44423</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>44424</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44424</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>44425</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44431</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44434</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44434</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>44434</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>44435</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>44435</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44435</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44438</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44439</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44439</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44440</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44445</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>44446</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44448</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44448</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44448</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44449</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>44449</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>44450</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>44454</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44456</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44462</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44463</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44463</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44466</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44467</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44467</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44468</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44468</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44473</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44473</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>44475</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44480</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>44487</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44487</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>44487</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44488</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44488</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44489</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44490</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>44491</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44494</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44501</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>44505</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44505</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44508</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44509</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44509</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>44509</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44509</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44509</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44509</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44509</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44511</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>44512</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>44512</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44512</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44512</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44518</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44523</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44523</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44523</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44523</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44523</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44524</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44526</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44528</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44537</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44538</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>44538</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44543</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44546</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>44550</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44550</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44550</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44550</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44550</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44550</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44552</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44552</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>44552</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44557</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44564</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44564</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44564</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44564</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44564</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44572</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44574</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44580</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44580</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44580</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44580</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44581</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44581</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44581</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44582</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44582</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44587</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44596</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44602</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44602</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44603</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44606</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44607</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44607</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44607</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44608</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44608</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44610</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44615</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44616</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44616</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44620</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44623</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44624</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44627</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44627</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44629</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44629</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44629</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44629</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>44629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44634</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>44635</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>44641</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44641</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44643</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44644</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44649</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44649</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44655</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>44656</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44658</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44658</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44659</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44659</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44663</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44665</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44671</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>44671</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>44676</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>44678</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>44679</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44679</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44683</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>44686</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44698</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44699</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44709</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44711</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44719</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>44719</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44719</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44720</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>44734</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>44735</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44735</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44745</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44745</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44745</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44748</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44748</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44750</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44758</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44759</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44762</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44762</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44763</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44763</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44764</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44776</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44777</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44780</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44780</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44780</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44784</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44785</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>44787</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>44787</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44787</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>44787</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44787</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>44802</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>44806</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44806</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44810</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44812</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>44812</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44813</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44813</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44819</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>44819</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>44819</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>44820</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44820</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44820</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44823</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44823</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44823</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44824</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>44824</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>44825</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>44826</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44827</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44829</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44829</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44830</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44830</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44831</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44840</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44840</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44840</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>44846</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44846</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44846</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>44846</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>44846</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44852</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44853</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44853</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44854</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44858</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44861</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44861</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44862</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44864</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44866</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44867</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>44868</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>44868</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44868</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44662,7 +44662,7 @@
         <v>44872</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>44872</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>44875</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44876</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>44876</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>44876</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>44876</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>44879</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>44880</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>44880</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>44881</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>44881</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>44881</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>44881</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>44881</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44881</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44885</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>44886</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>44886</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44894</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>44894</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44894</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44895</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>44896</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44896</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44900</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>44900</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>44900</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>44900</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44909</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>44910</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>44910</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44911</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>44911</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>44916</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44916</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>44917</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44921</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>44924</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44929</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44936</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>44936</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44936</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44937</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>44938</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44938</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44943</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44943</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44943</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44943</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44945</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>44945</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44946</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44949</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>44950</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>44952</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44952</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>44952</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>44959</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>44960</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44970</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44973</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44976</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>44977</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>44977</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>44980</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44980</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44980</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>44980</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44982</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>44985</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>44988</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>44993</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>44993</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>44993</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>44994</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>44994</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44998</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44998</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44999</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>44999</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45000</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45005</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45005</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45006</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45009</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45012</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45012</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45012</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45012</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45013</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45015</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45021</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45025</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45029</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45029</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45033</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45033</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45033</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45033</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45033</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45035</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45037</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45040</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45040</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45040</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45040</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45040</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45041</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45041</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45041</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45044</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45050</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45050</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45050</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45056</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>45056</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45057</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>45058</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>45061</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45062</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45063</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45063</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45065</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45065</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45068</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45068</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45070</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45070</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45071</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45072</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45075</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45078</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45078</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45079</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45081</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45082</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45082</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45085</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45085</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45086</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45089</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45089</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45092</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45092</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45093</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45093</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45095</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45096</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45096</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45098</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>45098</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45098</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45098</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45098</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45099</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>45099</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45099</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45099</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45099</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45099</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45105</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45105</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45106</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45106</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45106</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45106</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>45106</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45107</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45107</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45107</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45107</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45107</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45113</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45113</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>45113</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>45113</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45113</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45113</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45119</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45119</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45120</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45120</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45123</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45127</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45127</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45133</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45137</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45138</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45140</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45141</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45146</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45146</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45146</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45147</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45147</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45148</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45149</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45149</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>45149</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>45154</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45156</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>45156</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45156</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45159</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>45161</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>45161</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45162</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56665,7 +56665,7 @@
         <v>45164</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45167</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45168</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         <v>45168</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45168</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>45169</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45170</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45170</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45170</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45170</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45170</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45171</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45171</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45173</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45173</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45173</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45173</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>45176</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45176</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45180</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45180</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45183</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45186</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45189</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45189</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45189</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45189</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58229,7 +58229,7 @@
         <v>45189</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45189</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45189</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>45189</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58457,7 +58457,7 @@
         <v>45189</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>45191</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45191</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>45191</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45191</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>45194</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45194</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>45194</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45194</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>45197</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45201</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45202</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         <v>45203</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>45203</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45203</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>45203</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45204</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>45204</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45205</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         <v>45208</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45208</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45210</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45211</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45211</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45212</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45215</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45221</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>45222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45222</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         <v>45222</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45222</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>45223</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>45223</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45226</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45229</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>45229</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45231</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -60623,7 +60623,7 @@
         <v>45233</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -60673,14 +60673,14 @@
     <row r="1036" ht="15" customHeight="1">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>A 56452-2023</t>
+          <t>A 55274-2023</t>
         </is>
       </c>
       <c r="B1036" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -60693,7 +60693,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="H1036" t="n">
         <v>0</v>
@@ -60730,14 +60730,14 @@
     <row r="1037" ht="15" customHeight="1">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>A 55274-2023</t>
+          <t>A 56479-2023</t>
         </is>
       </c>
       <c r="B1037" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         </is>
       </c>
       <c r="G1037" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -60787,14 +60787,14 @@
     <row r="1038" ht="15" customHeight="1">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>A 56475-2023</t>
+          <t>A 55223-2023</t>
         </is>
       </c>
       <c r="B1038" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         </is>
       </c>
       <c r="G1038" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="H1038" t="n">
         <v>0</v>
@@ -60844,14 +60844,14 @@
     <row r="1039" ht="15" customHeight="1">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>A 55223-2023</t>
+          <t>A 56475-2023</t>
         </is>
       </c>
       <c r="B1039" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -60901,14 +60901,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 56506-2023</t>
+          <t>A 56485-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -60921,7 +60921,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -60958,14 +60958,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 56479-2023</t>
+          <t>A 56506-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -61015,14 +61015,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 56489-2023</t>
+          <t>A 56452-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61035,7 +61035,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>2.7</v>
+        <v>7.1</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -61079,7 +61079,7 @@
         <v>45237</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61129,14 +61129,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 56485-2023</t>
+          <t>A 56489-2023</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -61193,7 +61193,7 @@
         <v>45238</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>45239</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -61307,7 +61307,7 @@
         <v>45239</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45239</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>45242</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -61478,7 +61478,7 @@
         <v>45245</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -61540,7 +61540,7 @@
         <v>45246</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -61597,7 +61597,7 @@
         <v>45246</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -61654,7 +61654,7 @@
         <v>45249</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>45251</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -61768,7 +61768,7 @@
         <v>45251</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -61830,7 +61830,7 @@
         <v>45251</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -61887,7 +61887,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -61937,14 +61937,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 59312-2023</t>
+          <t>A 59203-2023</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -61957,7 +61957,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>8.699999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -61994,14 +61994,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59203-2023</t>
+          <t>A 59216-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -62051,14 +62051,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 59216-2023</t>
+          <t>A 59438-2023</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>2.1</v>
+        <v>19.9</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -62108,14 +62108,14 @@
     <row r="1061" ht="15" customHeight="1">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>A 59438-2023</t>
+          <t>A 59312-2023</t>
         </is>
       </c>
       <c r="B1061" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         </is>
       </c>
       <c r="G1061" t="n">
-        <v>19.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -62165,14 +62165,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 60018-2023</t>
+          <t>A 60019-2023</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62185,7 +62185,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -62222,14 +62222,14 @@
     <row r="1063" ht="15" customHeight="1">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>A 60019-2023</t>
+          <t>A 60018-2023</t>
         </is>
       </c>
       <c r="B1063" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         </is>
       </c>
       <c r="G1063" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>
@@ -62276,62 +62276,119 @@
       </c>
       <c r="R1063" s="2" t="inlineStr"/>
     </row>
-    <row r="1064">
+    <row r="1064" ht="15" customHeight="1">
       <c r="A1064" t="inlineStr">
         <is>
+          <t>A 61643-2023</t>
+        </is>
+      </c>
+      <c r="B1064" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C1064" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>SÄFFLE</t>
+        </is>
+      </c>
+      <c r="G1064" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1064" s="2" t="inlineStr"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
           <t>A 61223-2023</t>
         </is>
       </c>
-      <c r="B1064" s="1" t="n">
+      <c r="B1065" s="1" t="n">
         <v>45264</v>
       </c>
-      <c r="C1064" s="1" t="n">
-        <v>45265</v>
-      </c>
-      <c r="D1064" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E1064" t="inlineStr">
-        <is>
-          <t>SÄFFLE</t>
-        </is>
-      </c>
-      <c r="G1064" t="n">
+      <c r="C1065" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>SÄFFLE</t>
+        </is>
+      </c>
+      <c r="G1065" t="n">
         <v>4.3</v>
       </c>
-      <c r="H1064" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1064" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1064" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1064" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1064" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1064" t="n">
-        <v>0</v>
-      </c>
-      <c r="N1064" t="n">
-        <v>0</v>
-      </c>
-      <c r="O1064" t="n">
-        <v>0</v>
-      </c>
-      <c r="P1064" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q1064" t="n">
-        <v>0</v>
-      </c>
-      <c r="R1064" s="2" t="inlineStr"/>
+      <c r="H1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1065" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1071"/>
+  <dimension ref="A1:Y1072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>43598</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>45203</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>43360</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44452</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45203</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>43382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43431</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43461</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43594</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>43882</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44043</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44148</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44221</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44446</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44450</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44589</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44755</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44762</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44805</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44813</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44886</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44894</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44938</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45016</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>43319</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>43319</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>43325</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>43327</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>43327</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>43332</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>43340</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>43341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>43346</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>43348</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>43349</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43350</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>43353</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>43353</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>43353</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>43360</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>43361</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>43362</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>43363</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43369</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>43370</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>43374</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43374</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>43374</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>43374</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>43382</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>43390</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>43390</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>43392</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>43392</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>43392</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>43392</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>43392</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>43392</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>43395</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>43397</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>43405</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>43405</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>43406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>43410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43416</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>43416</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>43416</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>43416</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>43416</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>43419</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43419</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>43419</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43431</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43437</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>43445</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>43453</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>43461</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>43461</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>43462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>43467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>43467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>43475</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>43476</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>43479</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>43479</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>43483</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>43485</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>43487</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>43490</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>43493</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>43494</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>43494</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>43494</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>43494</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>43494</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>43502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>43502</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>43507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>43507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>43515</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>43515</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>43524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>43528</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>43542</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43544</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43546</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43547</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>43547</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>43559</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>43560</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>43563</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>43566</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>43567</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>43570</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43570</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>43578</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>43581</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>43584</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>43584</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>43584</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43591</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>43594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>43594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>43594</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43594</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>43594</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43594</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43594</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43594</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43598</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>43598</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>43598</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>43598</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>43598</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>43605</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>43606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>43606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>43606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>43606</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>43607</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>43612</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>43615</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>43629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>43635</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>43636</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43640</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>43644</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>43648</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>43648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>43648</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>43648</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>43653</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>43654</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>43656</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>43658</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>43665</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>43672</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>43676</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>43676</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>43684</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>43700</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>43713</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>43720</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>43725</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>43727</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>43732</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43733</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43738</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43738</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43740</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>43741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43742</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>43742</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>43746</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>43749</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>43753</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43754</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43766</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>43768</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>43770</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>43773</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43774</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43785</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43788</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43789</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43794</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43797</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43803</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43808</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43808</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43808</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43808</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43808</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43808</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43811</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43837</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43838</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43838</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43838</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>43844</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>43845</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>43845</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>43846</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43847</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43848</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43850</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43850</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43851</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43853</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43857</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43857</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43861</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43864</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43866</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43870</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43878</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43879</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43881</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43883</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43888</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43891</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43891</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43894</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>43895</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>43895</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>43896</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>43899</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>43899</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43899</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43901</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43905</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43906</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>43907</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>43907</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43910</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43913</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>43913</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>43913</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>43913</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>43913</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>43913</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>43913</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>43916</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>43916</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>43916</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>43920</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>43921</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>43922</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>43923</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>43923</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>43945</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>43945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>43956</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>43968</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>43978</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>43978</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>43983</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>43983</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>43997</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>43997</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44004</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44004</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44014</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44026</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44032</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44040</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44040</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44050</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44050</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44050</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44053</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44053</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44057</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44064</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44067</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44069</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44070</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44076</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44076</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44082</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44084</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44090</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44092</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44095</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44100</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44102</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44102</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44103</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44103</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44105</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44106</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44110</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44112</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44112</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44112</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44117</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44124</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44124</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44124</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44127</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44130</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44130</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44134</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44137</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44137</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44139</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44144</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44145</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44145</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44146</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44154</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44155</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44161</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44161</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44161</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44168</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>44175</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44183</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44189</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44193</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44193</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44193</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44204</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44206</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44207</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44208</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44209</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44211</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44216</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44217</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44218</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44221</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44221</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44221</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44221</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44221</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44221</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>44221</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44223</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44223</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44224</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44229</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44229</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44231</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44235</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44238</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44242</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44246</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44247</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44251</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44263</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44264</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44266</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44270</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44271</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44280</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44284</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44285</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44287</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44294</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44299</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>44301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44307</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44316</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44319</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44321</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44321</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44322</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44322</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>44328</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44333</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>44334</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44334</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>44340</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>44343</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44344</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44344</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>44347</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>44347</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44351</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44354</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>44358</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44362</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>44362</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44368</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44368</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44370</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>44377</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44378</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44378</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44378</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44378</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44385</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44385</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44385</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>44385</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44385</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44386</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>44389</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44389</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44389</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>44389</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>44389</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>44389</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>44389</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>44392</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>44392</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>44392</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44392</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44392</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44392</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>44392</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44392</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>44392</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>44392</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>44400</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>44403</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44404</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44412</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44417</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44418</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>44419</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44419</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44419</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44421</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>44423</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>44424</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44424</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>44425</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44431</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44434</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44434</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>44434</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>44435</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>44435</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44435</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44438</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44439</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44439</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44440</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44445</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>44446</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44448</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44448</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44448</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>44449</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>44449</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>44450</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>44454</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44456</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44462</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44463</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44463</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44466</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44467</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44467</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44468</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44468</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44473</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>44473</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>44475</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44480</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>44487</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44487</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>44487</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44488</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>44488</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44489</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44490</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>44491</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44494</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44501</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>44505</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44505</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44508</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>44509</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44509</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>44509</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44509</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44509</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44509</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44509</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44511</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>44512</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>44512</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44512</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44512</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44518</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44523</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44523</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44523</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44523</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44523</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44524</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44526</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44528</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44537</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44538</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>44538</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35177,7 +35177,7 @@
         <v>44543</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44546</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>44550</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44550</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>44550</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44550</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44550</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44550</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44552</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44552</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>44552</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44557</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44564</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44564</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44564</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44564</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44564</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44572</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44574</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44580</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44580</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44580</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44580</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44581</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44581</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44581</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44582</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44582</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44587</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44596</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44602</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44602</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44603</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44606</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44607</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44607</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44607</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44608</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44608</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44610</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44615</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44616</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44616</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44620</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44623</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44624</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44627</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44627</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44629</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>44629</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>44629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>44629</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44629</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>44629</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44634</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>44635</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>44641</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44641</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>44643</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>44644</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44649</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>44649</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44655</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>44656</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>44658</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44658</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44659</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>44659</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44663</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44665</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>44671</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>44671</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>44676</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>44678</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>44679</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>44679</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44683</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>44686</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>44698</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44699</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44709</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>44711</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>44719</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         <v>44719</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>44719</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44720</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>44734</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>44735</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>44735</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44745</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44745</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44745</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44748</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44748</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44750</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44758</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44759</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44762</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44762</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44763</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>44763</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44764</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44776</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44777</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44780</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44780</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>44780</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         <v>44784</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44785</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>44787</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>44787</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44787</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>44787</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44787</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>44802</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>44806</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44806</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44810</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44812</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>44812</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44813</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>44813</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44819</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>44819</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>44819</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>44820</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44820</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44820</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44823</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44823</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>44823</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44824</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>44824</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>44825</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>44826</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44827</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44829</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44829</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44830</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>44830</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>44831</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>44840</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44840</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44840</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>44846</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44846</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>44846</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>44846</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>44846</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44852</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44852</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44853</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44853</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44854</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44858</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>44861</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>44861</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>44862</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44864</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44866</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>44867</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>44868</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>44868</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44868</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44662,7 +44662,7 @@
         <v>44872</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>44872</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>44875</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>44876</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>44876</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>44876</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>44876</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>44879</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>44880</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>44880</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
         <v>44881</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>44881</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>44881</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>44881</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>44881</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44881</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44885</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>44886</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>44886</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44894</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>44894</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44894</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44895</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>44896</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44896</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44900</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>44900</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>44900</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>44900</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>44909</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>44910</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>44910</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>44911</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>44911</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>44916</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44916</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>44917</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44921</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>44924</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44929</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44936</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>44936</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>44936</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>44937</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>44938</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44938</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44943</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44943</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>44943</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44943</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44945</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>44945</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>44946</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44949</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>44950</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>44952</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>44952</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>44952</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>44959</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>44960</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44970</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44973</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>44976</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>44977</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>44977</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>44980</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44980</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44980</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>44980</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44982</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>44985</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>44988</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>44993</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>44993</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>44993</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>44994</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>44994</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44998</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44998</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>44999</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>44999</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45000</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45005</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45005</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45006</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45009</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45012</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45012</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45012</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45012</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45013</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45015</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45021</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45025</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45029</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45029</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45033</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45033</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45033</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45033</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45033</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45035</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45037</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45040</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45040</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45040</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45040</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45040</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45041</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45041</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45041</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45044</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45050</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45050</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45050</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45056</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>45056</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45057</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51505,7 +51505,7 @@
         <v>45058</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51562,7 +51562,7 @@
         <v>45061</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45062</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45063</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45063</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45065</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45065</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45068</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45068</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45070</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52075,7 +52075,7 @@
         <v>45070</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>45071</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45072</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45075</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45078</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45078</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45079</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45081</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45082</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>45082</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45085</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45085</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45086</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45089</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52878,7 +52878,7 @@
         <v>45089</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>45092</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45092</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45093</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>45093</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45095</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45096</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45096</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45098</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>45098</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45098</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45098</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45098</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45099</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>45099</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45099</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45099</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45099</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45099</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45105</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45105</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45106</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45106</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45106</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45106</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>45106</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45107</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>45107</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45107</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>45107</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54608,7 +54608,7 @@
         <v>45107</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>45113</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>45113</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>45113</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>45113</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45113</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45113</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45119</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45119</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45120</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45120</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45123</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45127</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45127</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45133</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45137</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45138</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45140</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45141</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45146</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>45146</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45146</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45147</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45147</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45148</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45149</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45149</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>45149</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>45154</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>45156</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56323,7 +56323,7 @@
         <v>45156</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>45156</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>45159</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>45161</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>45161</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45162</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56665,7 +56665,7 @@
         <v>45164</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45167</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45168</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         <v>45168</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45168</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>45169</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45170</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45170</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45170</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45170</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45170</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45171</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45171</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57421,7 +57421,7 @@
         <v>45173</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45173</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>45173</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45173</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>45176</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45176</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45180</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45180</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45183</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>45186</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>45189</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45189</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45189</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45189</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58229,7 +58229,7 @@
         <v>45189</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45189</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45189</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>45189</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58457,7 +58457,7 @@
         <v>45189</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>45191</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45191</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -58628,7 +58628,7 @@
         <v>45191</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>45191</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45191</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>45194</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45194</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>45194</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -58970,7 +58970,7 @@
         <v>45194</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>45197</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45201</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45202</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -59198,7 +59198,7 @@
         <v>45203</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -59255,7 +59255,7 @@
         <v>45203</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45203</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>45203</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45204</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -59483,7 +59483,7 @@
         <v>45204</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45205</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -59597,7 +59597,7 @@
         <v>45208</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45208</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45210</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45211</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45211</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45212</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45215</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45221</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>45222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45222</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         <v>45222</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45222</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>45223</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>45223</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45226</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45229</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>45229</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45231</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -60623,7 +60623,7 @@
         <v>45233</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>45237</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>45237</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -60794,7 +60794,7 @@
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -60851,7 +60851,7 @@
         <v>45237</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -60908,7 +60908,7 @@
         <v>45237</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -60965,7 +60965,7 @@
         <v>45237</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -61022,7 +61022,7 @@
         <v>45237</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -61079,7 +61079,7 @@
         <v>45237</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -61136,7 +61136,7 @@
         <v>45237</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -61193,7 +61193,7 @@
         <v>45238</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>45239</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -61307,7 +61307,7 @@
         <v>45239</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45239</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>45242</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -61478,7 +61478,7 @@
         <v>45245</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -61533,14 +61533,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 57544-2023</t>
+          <t>A 57577-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -61553,7 +61553,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -61590,14 +61590,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 57577-2023</t>
+          <t>A 57544-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -61610,7 +61610,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -61654,7 +61654,7 @@
         <v>45249</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>45251</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -61768,7 +61768,7 @@
         <v>45251</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -61825,7 +61825,7 @@
         <v>45251</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -61887,7 +61887,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -61937,14 +61937,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 59438-2023</t>
+          <t>A 59203-2023</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -61957,7 +61957,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>19.9</v>
+        <v>4.8</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -61994,14 +61994,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59312-2023</t>
+          <t>A 59216-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -62014,7 +62014,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>8.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -62051,14 +62051,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 59203-2023</t>
+          <t>A 59312-2023</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>4.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -62108,14 +62108,14 @@
     <row r="1061" ht="15" customHeight="1">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>A 59216-2023</t>
+          <t>A 59438-2023</t>
         </is>
       </c>
       <c r="B1061" s="1" t="n">
         <v>45253</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         </is>
       </c>
       <c r="G1061" t="n">
-        <v>2.1</v>
+        <v>19.9</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -62172,7 +62172,7 @@
         <v>45258</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45258</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -62286,7 +62286,7 @@
         <v>45261</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>45264</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -62400,7 +62400,7 @@
         <v>45266</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>45266</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -62514,7 +62514,7 @@
         <v>45266</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -62571,7 +62571,7 @@
         <v>45266</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -62628,7 +62628,7 @@
         <v>45267</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
       </c>
       <c r="R1070" s="2" t="inlineStr"/>
     </row>
-    <row r="1071">
+    <row r="1071" ht="15" customHeight="1">
       <c r="A1071" t="inlineStr">
         <is>
           <t>A 62298-2023</t>
@@ -62685,7 +62685,7 @@
         <v>45267</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -62731,6 +62731,63 @@
         <v>0</v>
       </c>
       <c r="R1071" s="2" t="inlineStr"/>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>A 62460-2023</t>
+        </is>
+      </c>
+      <c r="B1072" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="C1072" s="1" t="n">
+        <v>45269</v>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>SÄFFLE</t>
+        </is>
+      </c>
+      <c r="G1072" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1072" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -564,7 +564,7 @@
         <v>43598</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>45203</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>43360</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>44452</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>45203</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>43382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>43431</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>43461</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>43594</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>43882</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44043</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>44148</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>44221</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>44446</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44450</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44589</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>44755</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>44762</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44805</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44813</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>44886</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44894</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44938</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45016</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>43319</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>43319</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>43325</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>43327</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>43327</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>43332</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>43340</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>43341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>43346</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>43348</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>43349</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43350</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>43350</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>43353</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>43353</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>43353</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>43360</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>43361</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>43362</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>43363</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>43369</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>43370</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>43374</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>43374</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>43374</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>43374</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>43381</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>43382</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>43390</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>43390</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>43391</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>43392</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>43392</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>43392</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>43392</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>43392</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>43392</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>43395</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>43397</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>43405</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>43405</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>43406</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>43410</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>43416</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>43416</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>43416</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>43416</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>43416</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>43419</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43419</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>43419</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>43430</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>43431</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>43431</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>43431</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>43431</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>43433</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>43434</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>43437</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>43445</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>43451</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>43453</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>43454</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>43454</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>43461</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>43461</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>43462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>43467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>43467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>43472</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>43472</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>43475</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>43475</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>43476</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>43479</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>43479</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>43483</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>43483</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>43485</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>43487</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>43490</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>43493</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>43494</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>43494</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>43494</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>43494</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>43494</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>43502</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>43502</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>43507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>43507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>43515</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>43515</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>43523</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>43524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>43528</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>43532</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>43542</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>43542</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43544</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43544</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43546</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43547</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>43547</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>43557</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>43557</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>43559</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>43560</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>43563</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>43566</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>43567</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>43570</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>43570</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>43578</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>43581</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>43584</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>43584</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>43584</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>43591</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>43594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>43594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>43594</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43594</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>43594</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43594</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43594</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43594</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43594</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43594</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>43598</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>43598</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>43598</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>43598</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>43598</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>43605</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>43606</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>43606</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>43606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>43606</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>43607</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>43612</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>43615</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>43629</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>43635</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>43636</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43640</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>43644</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>43648</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>43648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>43648</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>43648</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>43651</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>43653</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>43654</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>43654</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>43656</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43658</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>43658</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>43665</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>43672</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>43676</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>43676</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>43684</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>43700</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>43713</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>43713</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>43720</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>43725</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>43727</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>43732</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>43733</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>43738</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>43738</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>43740</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>43741</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43741</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43742</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>43742</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>43746</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>43749</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>43753</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>43754</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>43766</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>43768</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>43770</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>43773</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43774</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43785</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43788</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43789</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43794</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43797</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43798</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>43803</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>43805</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>43808</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>43808</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>43808</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>43808</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>43808</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>43808</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43811</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43837</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43838</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43838</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43838</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>43844</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>43845</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>43845</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>43846</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>43847</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43848</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43850</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43850</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>43851</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>43851</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>43852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>43853</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>43857</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>43857</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>43861</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>43864</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>43866</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>43867</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>43870</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>43875</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>43878</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>43879</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43881</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43883</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43888</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43891</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43891</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43894</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>43895</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>43895</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>43896</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>43899</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>43899</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43899</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43901</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43901</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43901</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43902</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43902</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43905</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43906</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>43907</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>43907</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43910</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43913</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>43913</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>43913</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>43913</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>43913</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>43913</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>43913</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>43916</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>43916</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>43916</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>43920</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>43921</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>43922</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>43923</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>43923</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>43945</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>43945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>43956</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>43968</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>43978</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>43978</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>43983</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>43983</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>43997</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>43997</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44004</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>44004</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44014</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44014</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44026</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44032</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44040</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44040</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44050</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44050</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44050</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44053</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44053</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44057</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44061</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44064</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44067</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44069</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44070</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44076</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>44076</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44082</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44084</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44090</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>44092</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44095</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44100</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>44102</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44102</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44103</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>44103</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>44105</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44106</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44110</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44112</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44112</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>44112</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44117</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44124</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44124</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44124</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44127</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44130</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>44130</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>44134</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>44137</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44137</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44139</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44144</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>44145</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44145</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44146</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>44148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44154</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44155</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>44161</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44161</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44161</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44168</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>44175</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44183</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>44189</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44193</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44193</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44193</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44204</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>44206</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44207</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44208</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>44209</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44211</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44216</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44217</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44218</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44221</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44221</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44221</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44221</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44221</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44221</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>44221</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>44223</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44223</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44224</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44229</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44229</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44230</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>44231</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44235</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44238</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44242</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44246</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44247</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44251</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44258</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44258</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44258</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44260</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44263</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44264</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44266</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44270</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44271</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44280</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44284</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44285</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44287</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44294</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44296</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>44299</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>44301</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44302</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44307</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44316</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44319</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44321</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44321</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>44322</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44322</v>
       </